--- a/Forecasting_the_exports_volume_of_processed_seafood_in_Thailand/DATA/Export 2007-2024.xlsx
+++ b/Forecasting_the_exports_volume_of_processed_seafood_in_Thailand/DATA/Export 2007-2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noxra\KMUTNB_internship\DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noxra\KMUTNB_internship\Forecasting_the_exports_volume_of_processed_seafood_in_Thailand\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F422429-BE09-4B0B-80D3-2C77F4C426E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EA2281-1524-4DAA-B07D-57A0DEEBE55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>Year (พ.ศ.)</t>
   </si>
@@ -211,6 +211,27 @@
   </si>
   <si>
     <t>Grand Total Value (Million Baht)</t>
+  </si>
+  <si>
+    <t>Marine Fish (Tons)</t>
+  </si>
+  <si>
+    <t>Marine Shrimp (Tons)</t>
+  </si>
+  <si>
+    <t>Marine Crabs (Tons)</t>
+  </si>
+  <si>
+    <t>Marine Squid (Tons)</t>
+  </si>
+  <si>
+    <t>Marine Shellfish (Tons)</t>
+  </si>
+  <si>
+    <t>Other MarineAnimals (Tons)</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
   </si>
 </sst>
 </file>
@@ -1936,10 +1957,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BJ217"/>
+  <dimension ref="A1:BQ217"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:62" ht="211.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:69" ht="211.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="230" t="s">
         <v>0</v>
       </c>
@@ -2126,8 +2147,29 @@
       <c r="BJ1" s="24" t="s">
         <v>61</v>
       </c>
+      <c r="BK1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="2" spans="1:62" ht="21.6" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:69" ht="21.6" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="233">
         <v>2550</v>
       </c>
@@ -2310,8 +2352,29 @@
       <c r="BJ2" s="35">
         <v>14562.65</v>
       </c>
+      <c r="BK2">
+        <v>153158.29999999999</v>
+      </c>
+      <c r="BL2">
+        <v>48883.3</v>
+      </c>
+      <c r="BM2">
+        <v>2925</v>
+      </c>
+      <c r="BN2">
+        <v>10983.3</v>
+      </c>
+      <c r="BO2">
+        <v>27075</v>
+      </c>
+      <c r="BP2">
+        <v>700</v>
+      </c>
+      <c r="BQ2">
+        <v>243724.9</v>
+      </c>
     </row>
-    <row r="3" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A3" s="233">
         <v>2550</v>
       </c>
@@ -2494,8 +2557,29 @@
       <c r="BJ3" s="45">
         <v>15295.19</v>
       </c>
+      <c r="BK3">
+        <v>153158.29999999999</v>
+      </c>
+      <c r="BL3">
+        <v>48883.3</v>
+      </c>
+      <c r="BM3">
+        <v>2925</v>
+      </c>
+      <c r="BN3">
+        <v>10983.3</v>
+      </c>
+      <c r="BO3">
+        <v>27075</v>
+      </c>
+      <c r="BP3">
+        <v>700</v>
+      </c>
+      <c r="BQ3">
+        <v>243724.9</v>
+      </c>
     </row>
-    <row r="4" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A4" s="233">
         <v>2550</v>
       </c>
@@ -2678,8 +2762,29 @@
       <c r="BJ4" s="45">
         <v>17811.330000000002</v>
       </c>
+      <c r="BK4">
+        <v>153158.29999999999</v>
+      </c>
+      <c r="BL4">
+        <v>48883.3</v>
+      </c>
+      <c r="BM4">
+        <v>2925</v>
+      </c>
+      <c r="BN4">
+        <v>10983.3</v>
+      </c>
+      <c r="BO4">
+        <v>27075</v>
+      </c>
+      <c r="BP4">
+        <v>700</v>
+      </c>
+      <c r="BQ4">
+        <v>243724.9</v>
+      </c>
     </row>
-    <row r="5" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A5" s="233">
         <v>2550</v>
       </c>
@@ -2862,8 +2967,29 @@
       <c r="BJ5" s="45">
         <v>14369.74</v>
       </c>
+      <c r="BK5">
+        <v>153158.29999999999</v>
+      </c>
+      <c r="BL5">
+        <v>48883.3</v>
+      </c>
+      <c r="BM5">
+        <v>2925</v>
+      </c>
+      <c r="BN5">
+        <v>10983.3</v>
+      </c>
+      <c r="BO5">
+        <v>27075</v>
+      </c>
+      <c r="BP5">
+        <v>700</v>
+      </c>
+      <c r="BQ5">
+        <v>243724.9</v>
+      </c>
     </row>
-    <row r="6" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A6" s="233">
         <v>2550</v>
       </c>
@@ -3046,8 +3172,29 @@
       <c r="BJ6" s="45">
         <v>17047.87</v>
       </c>
+      <c r="BK6">
+        <v>153158.29999999999</v>
+      </c>
+      <c r="BL6">
+        <v>48883.3</v>
+      </c>
+      <c r="BM6">
+        <v>2925</v>
+      </c>
+      <c r="BN6">
+        <v>10983.3</v>
+      </c>
+      <c r="BO6">
+        <v>27075</v>
+      </c>
+      <c r="BP6">
+        <v>700</v>
+      </c>
+      <c r="BQ6">
+        <v>243724.9</v>
+      </c>
     </row>
-    <row r="7" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A7" s="233">
         <v>2550</v>
       </c>
@@ -3230,8 +3377,29 @@
       <c r="BJ7" s="45">
         <v>16817.580000000002</v>
       </c>
+      <c r="BK7">
+        <v>153158.29999999999</v>
+      </c>
+      <c r="BL7">
+        <v>48883.3</v>
+      </c>
+      <c r="BM7">
+        <v>2925</v>
+      </c>
+      <c r="BN7">
+        <v>10983.3</v>
+      </c>
+      <c r="BO7">
+        <v>27075</v>
+      </c>
+      <c r="BP7">
+        <v>700</v>
+      </c>
+      <c r="BQ7">
+        <v>243724.9</v>
+      </c>
     </row>
-    <row r="8" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A8" s="233">
         <v>2550</v>
       </c>
@@ -3414,8 +3582,29 @@
       <c r="BJ8" s="45">
         <v>16511.490000000002</v>
       </c>
+      <c r="BK8">
+        <v>153158.29999999999</v>
+      </c>
+      <c r="BL8">
+        <v>48883.3</v>
+      </c>
+      <c r="BM8">
+        <v>2925</v>
+      </c>
+      <c r="BN8">
+        <v>10983.3</v>
+      </c>
+      <c r="BO8">
+        <v>27075</v>
+      </c>
+      <c r="BP8">
+        <v>700</v>
+      </c>
+      <c r="BQ8">
+        <v>243724.9</v>
+      </c>
     </row>
-    <row r="9" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A9" s="233">
         <v>2550</v>
       </c>
@@ -3598,8 +3787,29 @@
       <c r="BJ9" s="45">
         <v>18631.689999999999</v>
       </c>
+      <c r="BK9">
+        <v>153158.29999999999</v>
+      </c>
+      <c r="BL9">
+        <v>48883.3</v>
+      </c>
+      <c r="BM9">
+        <v>2925</v>
+      </c>
+      <c r="BN9">
+        <v>10983.3</v>
+      </c>
+      <c r="BO9">
+        <v>27075</v>
+      </c>
+      <c r="BP9">
+        <v>700</v>
+      </c>
+      <c r="BQ9">
+        <v>243724.9</v>
+      </c>
     </row>
-    <row r="10" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A10" s="233">
         <v>2550</v>
       </c>
@@ -3782,8 +3992,29 @@
       <c r="BJ10" s="45">
         <v>18730.71</v>
       </c>
+      <c r="BK10">
+        <v>153158.29999999999</v>
+      </c>
+      <c r="BL10">
+        <v>48883.3</v>
+      </c>
+      <c r="BM10">
+        <v>2925</v>
+      </c>
+      <c r="BN10">
+        <v>10983.3</v>
+      </c>
+      <c r="BO10">
+        <v>27075</v>
+      </c>
+      <c r="BP10">
+        <v>700</v>
+      </c>
+      <c r="BQ10">
+        <v>243724.9</v>
+      </c>
     </row>
-    <row r="11" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A11" s="233">
         <v>2550</v>
       </c>
@@ -3966,8 +4197,29 @@
       <c r="BJ11" s="45">
         <v>19519.5</v>
       </c>
+      <c r="BK11">
+        <v>153158.29999999999</v>
+      </c>
+      <c r="BL11">
+        <v>48883.3</v>
+      </c>
+      <c r="BM11">
+        <v>2925</v>
+      </c>
+      <c r="BN11">
+        <v>10983.3</v>
+      </c>
+      <c r="BO11">
+        <v>27075</v>
+      </c>
+      <c r="BP11">
+        <v>700</v>
+      </c>
+      <c r="BQ11">
+        <v>243724.9</v>
+      </c>
     </row>
-    <row r="12" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A12" s="233">
         <v>2550</v>
       </c>
@@ -4150,8 +4402,29 @@
       <c r="BJ12" s="45">
         <v>19822.48</v>
       </c>
+      <c r="BK12">
+        <v>153158.29999999999</v>
+      </c>
+      <c r="BL12">
+        <v>48883.3</v>
+      </c>
+      <c r="BM12">
+        <v>2925</v>
+      </c>
+      <c r="BN12">
+        <v>10983.3</v>
+      </c>
+      <c r="BO12">
+        <v>27075</v>
+      </c>
+      <c r="BP12">
+        <v>700</v>
+      </c>
+      <c r="BQ12">
+        <v>243724.9</v>
+      </c>
     </row>
-    <row r="13" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A13" s="233">
         <v>2550</v>
       </c>
@@ -4334,8 +4607,29 @@
       <c r="BJ13" s="45">
         <v>16746.47</v>
       </c>
+      <c r="BK13">
+        <v>153158.29999999999</v>
+      </c>
+      <c r="BL13">
+        <v>48883.3</v>
+      </c>
+      <c r="BM13">
+        <v>2925</v>
+      </c>
+      <c r="BN13">
+        <v>10983.3</v>
+      </c>
+      <c r="BO13">
+        <v>27075</v>
+      </c>
+      <c r="BP13">
+        <v>700</v>
+      </c>
+      <c r="BQ13">
+        <v>243724.9</v>
+      </c>
     </row>
-    <row r="14" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A14" s="235">
         <v>2551</v>
       </c>
@@ -4518,8 +4812,29 @@
       <c r="BJ14" s="58">
         <v>16057.08</v>
       </c>
+      <c r="BK14">
+        <v>107741.6</v>
+      </c>
+      <c r="BL14">
+        <v>46716.6</v>
+      </c>
+      <c r="BM14">
+        <v>2541.6</v>
+      </c>
+      <c r="BN14">
+        <v>9416.6</v>
+      </c>
+      <c r="BO14">
+        <v>25508.3</v>
+      </c>
+      <c r="BP14">
+        <v>12500</v>
+      </c>
+      <c r="BQ14">
+        <v>204424.7</v>
+      </c>
     </row>
-    <row r="15" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A15" s="235">
         <v>2551</v>
       </c>
@@ -4702,8 +5017,29 @@
       <c r="BJ15" s="58">
         <v>15277.18</v>
       </c>
+      <c r="BK15">
+        <v>107741.6</v>
+      </c>
+      <c r="BL15">
+        <v>46716.6</v>
+      </c>
+      <c r="BM15">
+        <v>2541.6</v>
+      </c>
+      <c r="BN15">
+        <v>9416.6</v>
+      </c>
+      <c r="BO15">
+        <v>25508.3</v>
+      </c>
+      <c r="BP15">
+        <v>12500</v>
+      </c>
+      <c r="BQ15">
+        <v>204424.7</v>
+      </c>
     </row>
-    <row r="16" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A16" s="235">
         <v>2551</v>
       </c>
@@ -4886,8 +5222,29 @@
       <c r="BJ16" s="58">
         <v>16991.54</v>
       </c>
+      <c r="BK16">
+        <v>107741.6</v>
+      </c>
+      <c r="BL16">
+        <v>46716.6</v>
+      </c>
+      <c r="BM16">
+        <v>2541.6</v>
+      </c>
+      <c r="BN16">
+        <v>9416.6</v>
+      </c>
+      <c r="BO16">
+        <v>25508.3</v>
+      </c>
+      <c r="BP16">
+        <v>12500</v>
+      </c>
+      <c r="BQ16">
+        <v>204424.7</v>
+      </c>
     </row>
-    <row r="17" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A17" s="235">
         <v>2551</v>
       </c>
@@ -5070,8 +5427,29 @@
       <c r="BJ17" s="58">
         <v>16436.21</v>
       </c>
+      <c r="BK17">
+        <v>107741.6</v>
+      </c>
+      <c r="BL17">
+        <v>46716.6</v>
+      </c>
+      <c r="BM17">
+        <v>2541.6</v>
+      </c>
+      <c r="BN17">
+        <v>9416.6</v>
+      </c>
+      <c r="BO17">
+        <v>25508.3</v>
+      </c>
+      <c r="BP17">
+        <v>12500</v>
+      </c>
+      <c r="BQ17">
+        <v>204424.7</v>
+      </c>
     </row>
-    <row r="18" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A18" s="235">
         <v>2551</v>
       </c>
@@ -5254,8 +5632,29 @@
       <c r="BJ18" s="58">
         <v>18279.72</v>
       </c>
+      <c r="BK18">
+        <v>107741.6</v>
+      </c>
+      <c r="BL18">
+        <v>46716.6</v>
+      </c>
+      <c r="BM18">
+        <v>2541.6</v>
+      </c>
+      <c r="BN18">
+        <v>9416.6</v>
+      </c>
+      <c r="BO18">
+        <v>25508.3</v>
+      </c>
+      <c r="BP18">
+        <v>12500</v>
+      </c>
+      <c r="BQ18">
+        <v>204424.7</v>
+      </c>
     </row>
-    <row r="19" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A19" s="235">
         <v>2551</v>
       </c>
@@ -5438,8 +5837,29 @@
       <c r="BJ19" s="58">
         <v>18215.37</v>
       </c>
+      <c r="BK19">
+        <v>107741.6</v>
+      </c>
+      <c r="BL19">
+        <v>46716.6</v>
+      </c>
+      <c r="BM19">
+        <v>2541.6</v>
+      </c>
+      <c r="BN19">
+        <v>9416.6</v>
+      </c>
+      <c r="BO19">
+        <v>25508.3</v>
+      </c>
+      <c r="BP19">
+        <v>12500</v>
+      </c>
+      <c r="BQ19">
+        <v>204424.7</v>
+      </c>
     </row>
-    <row r="20" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A20" s="235">
         <v>2551</v>
       </c>
@@ -5622,8 +6042,29 @@
       <c r="BJ20" s="58">
         <v>21335.82</v>
       </c>
+      <c r="BK20">
+        <v>107741.6</v>
+      </c>
+      <c r="BL20">
+        <v>46716.6</v>
+      </c>
+      <c r="BM20">
+        <v>2541.6</v>
+      </c>
+      <c r="BN20">
+        <v>9416.6</v>
+      </c>
+      <c r="BO20">
+        <v>25508.3</v>
+      </c>
+      <c r="BP20">
+        <v>12500</v>
+      </c>
+      <c r="BQ20">
+        <v>204424.7</v>
+      </c>
     </row>
-    <row r="21" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A21" s="235">
         <v>2551</v>
       </c>
@@ -5806,8 +6247,29 @@
       <c r="BJ21" s="58">
         <v>21546.91</v>
       </c>
+      <c r="BK21">
+        <v>107741.6</v>
+      </c>
+      <c r="BL21">
+        <v>46716.6</v>
+      </c>
+      <c r="BM21">
+        <v>2541.6</v>
+      </c>
+      <c r="BN21">
+        <v>9416.6</v>
+      </c>
+      <c r="BO21">
+        <v>25508.3</v>
+      </c>
+      <c r="BP21">
+        <v>12500</v>
+      </c>
+      <c r="BQ21">
+        <v>204424.7</v>
+      </c>
     </row>
-    <row r="22" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A22" s="235">
         <v>2551</v>
       </c>
@@ -5990,8 +6452,29 @@
       <c r="BJ22" s="58">
         <v>21304.31</v>
       </c>
+      <c r="BK22">
+        <v>107741.6</v>
+      </c>
+      <c r="BL22">
+        <v>46716.6</v>
+      </c>
+      <c r="BM22">
+        <v>2541.6</v>
+      </c>
+      <c r="BN22">
+        <v>9416.6</v>
+      </c>
+      <c r="BO22">
+        <v>25508.3</v>
+      </c>
+      <c r="BP22">
+        <v>12500</v>
+      </c>
+      <c r="BQ22">
+        <v>204424.7</v>
+      </c>
     </row>
-    <row r="23" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A23" s="235">
         <v>2551</v>
       </c>
@@ -6174,8 +6657,29 @@
       <c r="BJ23" s="58">
         <v>23647.56</v>
       </c>
+      <c r="BK23">
+        <v>107741.6</v>
+      </c>
+      <c r="BL23">
+        <v>46716.6</v>
+      </c>
+      <c r="BM23">
+        <v>2541.6</v>
+      </c>
+      <c r="BN23">
+        <v>9416.6</v>
+      </c>
+      <c r="BO23">
+        <v>25508.3</v>
+      </c>
+      <c r="BP23">
+        <v>12500</v>
+      </c>
+      <c r="BQ23">
+        <v>204424.7</v>
+      </c>
     </row>
-    <row r="24" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A24" s="235">
         <v>2551</v>
       </c>
@@ -6358,8 +6862,29 @@
       <c r="BJ24" s="58">
         <v>20792.3</v>
       </c>
+      <c r="BK24">
+        <v>107741.6</v>
+      </c>
+      <c r="BL24">
+        <v>46716.6</v>
+      </c>
+      <c r="BM24">
+        <v>2541.6</v>
+      </c>
+      <c r="BN24">
+        <v>9416.6</v>
+      </c>
+      <c r="BO24">
+        <v>25508.3</v>
+      </c>
+      <c r="BP24">
+        <v>12500</v>
+      </c>
+      <c r="BQ24">
+        <v>204424.7</v>
+      </c>
     </row>
-    <row r="25" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A25" s="235">
         <v>2551</v>
       </c>
@@ -6542,8 +7067,29 @@
       <c r="BJ25" s="58">
         <v>18333.650000000001</v>
       </c>
+      <c r="BK25">
+        <v>107741.6</v>
+      </c>
+      <c r="BL25">
+        <v>46716.6</v>
+      </c>
+      <c r="BM25">
+        <v>2541.6</v>
+      </c>
+      <c r="BN25">
+        <v>9416.6</v>
+      </c>
+      <c r="BO25">
+        <v>25508.3</v>
+      </c>
+      <c r="BP25">
+        <v>12500</v>
+      </c>
+      <c r="BQ25">
+        <v>204424.7</v>
+      </c>
     </row>
-    <row r="26" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A26" s="237">
         <v>2552</v>
       </c>
@@ -6726,8 +7272,29 @@
       <c r="BJ26" s="71">
         <v>15085.79</v>
       </c>
+      <c r="BK26">
+        <v>112008.3</v>
+      </c>
+      <c r="BL26">
+        <v>52491.6</v>
+      </c>
+      <c r="BM26">
+        <v>2633.3</v>
+      </c>
+      <c r="BN26">
+        <v>9208.2999999999993</v>
+      </c>
+      <c r="BO26">
+        <v>27025</v>
+      </c>
+      <c r="BP26">
+        <v>9850</v>
+      </c>
+      <c r="BQ26">
+        <v>213216.5</v>
+      </c>
     </row>
-    <row r="27" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A27" s="237">
         <v>2552</v>
       </c>
@@ -6910,8 +7477,29 @@
       <c r="BJ27" s="71">
         <v>15226.44</v>
       </c>
+      <c r="BK27">
+        <v>112008.3</v>
+      </c>
+      <c r="BL27">
+        <v>52491.6</v>
+      </c>
+      <c r="BM27">
+        <v>2633.3</v>
+      </c>
+      <c r="BN27">
+        <v>9208.2999999999993</v>
+      </c>
+      <c r="BO27">
+        <v>27025</v>
+      </c>
+      <c r="BP27">
+        <v>9850</v>
+      </c>
+      <c r="BQ27">
+        <v>213216.5</v>
+      </c>
     </row>
-    <row r="28" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A28" s="237">
         <v>2552</v>
       </c>
@@ -7094,8 +7682,29 @@
       <c r="BJ28" s="71">
         <v>16837.8</v>
       </c>
+      <c r="BK28">
+        <v>112008.3</v>
+      </c>
+      <c r="BL28">
+        <v>52491.6</v>
+      </c>
+      <c r="BM28">
+        <v>2633.3</v>
+      </c>
+      <c r="BN28">
+        <v>9208.2999999999993</v>
+      </c>
+      <c r="BO28">
+        <v>27025</v>
+      </c>
+      <c r="BP28">
+        <v>9850</v>
+      </c>
+      <c r="BQ28">
+        <v>213216.5</v>
+      </c>
     </row>
-    <row r="29" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A29" s="237">
         <v>2552</v>
       </c>
@@ -7278,8 +7887,29 @@
       <c r="BJ29" s="71">
         <v>16995.099999999999</v>
       </c>
+      <c r="BK29">
+        <v>112008.3</v>
+      </c>
+      <c r="BL29">
+        <v>52491.6</v>
+      </c>
+      <c r="BM29">
+        <v>2633.3</v>
+      </c>
+      <c r="BN29">
+        <v>9208.2999999999993</v>
+      </c>
+      <c r="BO29">
+        <v>27025</v>
+      </c>
+      <c r="BP29">
+        <v>9850</v>
+      </c>
+      <c r="BQ29">
+        <v>213216.5</v>
+      </c>
     </row>
-    <row r="30" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A30" s="237">
         <v>2552</v>
       </c>
@@ -7462,8 +8092,29 @@
       <c r="BJ30" s="71">
         <v>18387.93</v>
       </c>
+      <c r="BK30">
+        <v>112008.3</v>
+      </c>
+      <c r="BL30">
+        <v>52491.6</v>
+      </c>
+      <c r="BM30">
+        <v>2633.3</v>
+      </c>
+      <c r="BN30">
+        <v>9208.2999999999993</v>
+      </c>
+      <c r="BO30">
+        <v>27025</v>
+      </c>
+      <c r="BP30">
+        <v>9850</v>
+      </c>
+      <c r="BQ30">
+        <v>213216.5</v>
+      </c>
     </row>
-    <row r="31" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A31" s="237">
         <v>2552</v>
       </c>
@@ -7646,8 +8297,29 @@
       <c r="BJ31" s="71">
         <v>18945.830000000002</v>
       </c>
+      <c r="BK31">
+        <v>112008.3</v>
+      </c>
+      <c r="BL31">
+        <v>52491.6</v>
+      </c>
+      <c r="BM31">
+        <v>2633.3</v>
+      </c>
+      <c r="BN31">
+        <v>9208.2999999999993</v>
+      </c>
+      <c r="BO31">
+        <v>27025</v>
+      </c>
+      <c r="BP31">
+        <v>9850</v>
+      </c>
+      <c r="BQ31">
+        <v>213216.5</v>
+      </c>
     </row>
-    <row r="32" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A32" s="237">
         <v>2552</v>
       </c>
@@ -7830,8 +8502,29 @@
       <c r="BJ32" s="71">
         <v>20722.89</v>
       </c>
+      <c r="BK32">
+        <v>112008.3</v>
+      </c>
+      <c r="BL32">
+        <v>52491.6</v>
+      </c>
+      <c r="BM32">
+        <v>2633.3</v>
+      </c>
+      <c r="BN32">
+        <v>9208.2999999999993</v>
+      </c>
+      <c r="BO32">
+        <v>27025</v>
+      </c>
+      <c r="BP32">
+        <v>9850</v>
+      </c>
+      <c r="BQ32">
+        <v>213216.5</v>
+      </c>
     </row>
-    <row r="33" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A33" s="237">
         <v>2552</v>
       </c>
@@ -8014,8 +8707,29 @@
       <c r="BJ33" s="71">
         <v>19484.169999999998</v>
       </c>
+      <c r="BK33">
+        <v>112008.3</v>
+      </c>
+      <c r="BL33">
+        <v>52491.6</v>
+      </c>
+      <c r="BM33">
+        <v>2633.3</v>
+      </c>
+      <c r="BN33">
+        <v>9208.2999999999993</v>
+      </c>
+      <c r="BO33">
+        <v>27025</v>
+      </c>
+      <c r="BP33">
+        <v>9850</v>
+      </c>
+      <c r="BQ33">
+        <v>213216.5</v>
+      </c>
     </row>
-    <row r="34" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A34" s="237">
         <v>2552</v>
       </c>
@@ -8198,8 +8912,29 @@
       <c r="BJ34" s="71">
         <v>21099.3</v>
       </c>
+      <c r="BK34">
+        <v>112008.3</v>
+      </c>
+      <c r="BL34">
+        <v>52491.6</v>
+      </c>
+      <c r="BM34">
+        <v>2633.3</v>
+      </c>
+      <c r="BN34">
+        <v>9208.2999999999993</v>
+      </c>
+      <c r="BO34">
+        <v>27025</v>
+      </c>
+      <c r="BP34">
+        <v>9850</v>
+      </c>
+      <c r="BQ34">
+        <v>213216.5</v>
+      </c>
     </row>
-    <row r="35" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A35" s="237">
         <v>2552</v>
       </c>
@@ -8382,8 +9117,29 @@
       <c r="BJ35" s="71">
         <v>22469.599999999999</v>
       </c>
+      <c r="BK35">
+        <v>112008.3</v>
+      </c>
+      <c r="BL35">
+        <v>52491.6</v>
+      </c>
+      <c r="BM35">
+        <v>2633.3</v>
+      </c>
+      <c r="BN35">
+        <v>9208.2999999999993</v>
+      </c>
+      <c r="BO35">
+        <v>27025</v>
+      </c>
+      <c r="BP35">
+        <v>9850</v>
+      </c>
+      <c r="BQ35">
+        <v>213216.5</v>
+      </c>
     </row>
-    <row r="36" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A36" s="237">
         <v>2552</v>
       </c>
@@ -8566,8 +9322,29 @@
       <c r="BJ36" s="71">
         <v>19982.599999999999</v>
       </c>
+      <c r="BK36">
+        <v>112008.3</v>
+      </c>
+      <c r="BL36">
+        <v>52491.6</v>
+      </c>
+      <c r="BM36">
+        <v>2633.3</v>
+      </c>
+      <c r="BN36">
+        <v>9208.2999999999993</v>
+      </c>
+      <c r="BO36">
+        <v>27025</v>
+      </c>
+      <c r="BP36">
+        <v>9850</v>
+      </c>
+      <c r="BQ36">
+        <v>213216.5</v>
+      </c>
     </row>
-    <row r="37" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A37" s="237">
         <v>2552</v>
       </c>
@@ -8750,8 +9527,29 @@
       <c r="BJ37" s="71">
         <v>19275.16</v>
       </c>
+      <c r="BK37">
+        <v>112008.3</v>
+      </c>
+      <c r="BL37">
+        <v>52491.6</v>
+      </c>
+      <c r="BM37">
+        <v>2633.3</v>
+      </c>
+      <c r="BN37">
+        <v>9208.2999999999993</v>
+      </c>
+      <c r="BO37">
+        <v>27025</v>
+      </c>
+      <c r="BP37">
+        <v>9850</v>
+      </c>
+      <c r="BQ37">
+        <v>213216.5</v>
+      </c>
     </row>
-    <row r="38" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A38" s="239">
         <v>2553</v>
       </c>
@@ -8934,8 +9732,29 @@
       <c r="BJ38" s="83">
         <v>16952.330000000002</v>
       </c>
+      <c r="BK38">
+        <v>112083.3</v>
+      </c>
+      <c r="BL38">
+        <v>51166.6</v>
+      </c>
+      <c r="BM38">
+        <v>2650</v>
+      </c>
+      <c r="BN38">
+        <v>10583.3</v>
+      </c>
+      <c r="BO38">
+        <v>16800</v>
+      </c>
+      <c r="BP38">
+        <v>3108.3</v>
+      </c>
+      <c r="BQ38">
+        <v>196391.5</v>
+      </c>
     </row>
-    <row r="39" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A39" s="239">
         <v>2553</v>
       </c>
@@ -9118,8 +9937,29 @@
       <c r="BJ39" s="83">
         <v>16616.150000000001</v>
       </c>
+      <c r="BK39">
+        <v>112083.3</v>
+      </c>
+      <c r="BL39">
+        <v>51166.6</v>
+      </c>
+      <c r="BM39">
+        <v>2650</v>
+      </c>
+      <c r="BN39">
+        <v>10583.3</v>
+      </c>
+      <c r="BO39">
+        <v>16800</v>
+      </c>
+      <c r="BP39">
+        <v>3108.3</v>
+      </c>
+      <c r="BQ39">
+        <v>196391.5</v>
+      </c>
     </row>
-    <row r="40" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A40" s="239">
         <v>2553</v>
       </c>
@@ -9302,8 +10142,29 @@
       <c r="BJ40" s="83">
         <v>19955.169999999998</v>
       </c>
+      <c r="BK40">
+        <v>112083.3</v>
+      </c>
+      <c r="BL40">
+        <v>51166.6</v>
+      </c>
+      <c r="BM40">
+        <v>2650</v>
+      </c>
+      <c r="BN40">
+        <v>10583.3</v>
+      </c>
+      <c r="BO40">
+        <v>16800</v>
+      </c>
+      <c r="BP40">
+        <v>3108.3</v>
+      </c>
+      <c r="BQ40">
+        <v>196391.5</v>
+      </c>
     </row>
-    <row r="41" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A41" s="239">
         <v>2553</v>
       </c>
@@ -9486,8 +10347,29 @@
       <c r="BJ41" s="83">
         <v>15998.3</v>
       </c>
+      <c r="BK41">
+        <v>112083.3</v>
+      </c>
+      <c r="BL41">
+        <v>51166.6</v>
+      </c>
+      <c r="BM41">
+        <v>2650</v>
+      </c>
+      <c r="BN41">
+        <v>10583.3</v>
+      </c>
+      <c r="BO41">
+        <v>16800</v>
+      </c>
+      <c r="BP41">
+        <v>3108.3</v>
+      </c>
+      <c r="BQ41">
+        <v>196391.5</v>
+      </c>
     </row>
-    <row r="42" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A42" s="239">
         <v>2553</v>
       </c>
@@ -9670,8 +10552,29 @@
       <c r="BJ42" s="83">
         <v>18623.64</v>
       </c>
+      <c r="BK42">
+        <v>112083.3</v>
+      </c>
+      <c r="BL42">
+        <v>51166.6</v>
+      </c>
+      <c r="BM42">
+        <v>2650</v>
+      </c>
+      <c r="BN42">
+        <v>10583.3</v>
+      </c>
+      <c r="BO42">
+        <v>16800</v>
+      </c>
+      <c r="BP42">
+        <v>3108.3</v>
+      </c>
+      <c r="BQ42">
+        <v>196391.5</v>
+      </c>
     </row>
-    <row r="43" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A43" s="239">
         <v>2553</v>
       </c>
@@ -9854,8 +10757,29 @@
       <c r="BJ43" s="83">
         <v>22790.23</v>
       </c>
+      <c r="BK43">
+        <v>112083.3</v>
+      </c>
+      <c r="BL43">
+        <v>51166.6</v>
+      </c>
+      <c r="BM43">
+        <v>2650</v>
+      </c>
+      <c r="BN43">
+        <v>10583.3</v>
+      </c>
+      <c r="BO43">
+        <v>16800</v>
+      </c>
+      <c r="BP43">
+        <v>3108.3</v>
+      </c>
+      <c r="BQ43">
+        <v>196391.5</v>
+      </c>
     </row>
-    <row r="44" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A44" s="239">
         <v>2553</v>
       </c>
@@ -10038,8 +10962,29 @@
       <c r="BJ44" s="83">
         <v>20850.78</v>
       </c>
+      <c r="BK44">
+        <v>112083.3</v>
+      </c>
+      <c r="BL44">
+        <v>51166.6</v>
+      </c>
+      <c r="BM44">
+        <v>2650</v>
+      </c>
+      <c r="BN44">
+        <v>10583.3</v>
+      </c>
+      <c r="BO44">
+        <v>16800</v>
+      </c>
+      <c r="BP44">
+        <v>3108.3</v>
+      </c>
+      <c r="BQ44">
+        <v>196391.5</v>
+      </c>
     </row>
-    <row r="45" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A45" s="239">
         <v>2553</v>
       </c>
@@ -10222,8 +11167,29 @@
       <c r="BJ45" s="83">
         <v>20175.84</v>
       </c>
+      <c r="BK45">
+        <v>112083.3</v>
+      </c>
+      <c r="BL45">
+        <v>51166.6</v>
+      </c>
+      <c r="BM45">
+        <v>2650</v>
+      </c>
+      <c r="BN45">
+        <v>10583.3</v>
+      </c>
+      <c r="BO45">
+        <v>16800</v>
+      </c>
+      <c r="BP45">
+        <v>3108.3</v>
+      </c>
+      <c r="BQ45">
+        <v>196391.5</v>
+      </c>
     </row>
-    <row r="46" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A46" s="239">
         <v>2553</v>
       </c>
@@ -10406,8 +11372,29 @@
       <c r="BJ46" s="83">
         <v>21309.7</v>
       </c>
+      <c r="BK46">
+        <v>112083.3</v>
+      </c>
+      <c r="BL46">
+        <v>51166.6</v>
+      </c>
+      <c r="BM46">
+        <v>2650</v>
+      </c>
+      <c r="BN46">
+        <v>10583.3</v>
+      </c>
+      <c r="BO46">
+        <v>16800</v>
+      </c>
+      <c r="BP46">
+        <v>3108.3</v>
+      </c>
+      <c r="BQ46">
+        <v>196391.5</v>
+      </c>
     </row>
-    <row r="47" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A47" s="239">
         <v>2553</v>
       </c>
@@ -10590,8 +11577,29 @@
       <c r="BJ47" s="83">
         <v>21922.23</v>
       </c>
+      <c r="BK47">
+        <v>112083.3</v>
+      </c>
+      <c r="BL47">
+        <v>51166.6</v>
+      </c>
+      <c r="BM47">
+        <v>2650</v>
+      </c>
+      <c r="BN47">
+        <v>10583.3</v>
+      </c>
+      <c r="BO47">
+        <v>16800</v>
+      </c>
+      <c r="BP47">
+        <v>3108.3</v>
+      </c>
+      <c r="BQ47">
+        <v>196391.5</v>
+      </c>
     </row>
-    <row r="48" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A48" s="239">
         <v>2553</v>
       </c>
@@ -10774,8 +11782,29 @@
       <c r="BJ48" s="83">
         <v>21191.200000000001</v>
       </c>
+      <c r="BK48">
+        <v>112083.3</v>
+      </c>
+      <c r="BL48">
+        <v>51166.6</v>
+      </c>
+      <c r="BM48">
+        <v>2650</v>
+      </c>
+      <c r="BN48">
+        <v>10583.3</v>
+      </c>
+      <c r="BO48">
+        <v>16800</v>
+      </c>
+      <c r="BP48">
+        <v>3108.3</v>
+      </c>
+      <c r="BQ48">
+        <v>196391.5</v>
+      </c>
     </row>
-    <row r="49" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A49" s="239">
         <v>2553</v>
       </c>
@@ -10958,8 +11987,29 @@
       <c r="BJ49" s="83">
         <v>20516.57</v>
       </c>
+      <c r="BK49">
+        <v>112083.3</v>
+      </c>
+      <c r="BL49">
+        <v>51166.6</v>
+      </c>
+      <c r="BM49">
+        <v>2650</v>
+      </c>
+      <c r="BN49">
+        <v>10583.3</v>
+      </c>
+      <c r="BO49">
+        <v>16800</v>
+      </c>
+      <c r="BP49">
+        <v>3108.3</v>
+      </c>
+      <c r="BQ49">
+        <v>196391.5</v>
+      </c>
     </row>
-    <row r="50" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A50" s="241">
         <v>2554</v>
       </c>
@@ -11142,8 +12192,29 @@
       <c r="BJ50" s="96">
         <v>16954.03</v>
       </c>
+      <c r="BK50">
+        <v>107716.6</v>
+      </c>
+      <c r="BL50">
+        <v>55000</v>
+      </c>
+      <c r="BM50">
+        <v>3000</v>
+      </c>
+      <c r="BN50">
+        <v>10700</v>
+      </c>
+      <c r="BO50">
+        <v>17075</v>
+      </c>
+      <c r="BP50">
+        <v>8791.6</v>
+      </c>
+      <c r="BQ50">
+        <v>202283.2</v>
+      </c>
     </row>
-    <row r="51" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A51" s="241">
         <v>2554</v>
       </c>
@@ -11326,8 +12397,29 @@
       <c r="BJ51" s="96">
         <v>17437.72</v>
       </c>
+      <c r="BK51">
+        <v>107716.6</v>
+      </c>
+      <c r="BL51">
+        <v>55000</v>
+      </c>
+      <c r="BM51">
+        <v>3000</v>
+      </c>
+      <c r="BN51">
+        <v>10700</v>
+      </c>
+      <c r="BO51">
+        <v>17075</v>
+      </c>
+      <c r="BP51">
+        <v>8791.6</v>
+      </c>
+      <c r="BQ51">
+        <v>202283.2</v>
+      </c>
     </row>
-    <row r="52" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A52" s="241">
         <v>2554</v>
       </c>
@@ -11510,8 +12602,29 @@
       <c r="BJ52" s="96">
         <v>21532.959999999999</v>
       </c>
+      <c r="BK52">
+        <v>107716.6</v>
+      </c>
+      <c r="BL52">
+        <v>55000</v>
+      </c>
+      <c r="BM52">
+        <v>3000</v>
+      </c>
+      <c r="BN52">
+        <v>10700</v>
+      </c>
+      <c r="BO52">
+        <v>17075</v>
+      </c>
+      <c r="BP52">
+        <v>8791.6</v>
+      </c>
+      <c r="BQ52">
+        <v>202283.2</v>
+      </c>
     </row>
-    <row r="53" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A53" s="241">
         <v>2554</v>
       </c>
@@ -11694,8 +12807,29 @@
       <c r="BJ53" s="96">
         <v>17814.04</v>
       </c>
+      <c r="BK53">
+        <v>107716.6</v>
+      </c>
+      <c r="BL53">
+        <v>55000</v>
+      </c>
+      <c r="BM53">
+        <v>3000</v>
+      </c>
+      <c r="BN53">
+        <v>10700</v>
+      </c>
+      <c r="BO53">
+        <v>17075</v>
+      </c>
+      <c r="BP53">
+        <v>8791.6</v>
+      </c>
+      <c r="BQ53">
+        <v>202283.2</v>
+      </c>
     </row>
-    <row r="54" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A54" s="241">
         <v>2554</v>
       </c>
@@ -11878,8 +13012,29 @@
       <c r="BJ54" s="96">
         <v>20535.39</v>
       </c>
+      <c r="BK54">
+        <v>107716.6</v>
+      </c>
+      <c r="BL54">
+        <v>55000</v>
+      </c>
+      <c r="BM54">
+        <v>3000</v>
+      </c>
+      <c r="BN54">
+        <v>10700</v>
+      </c>
+      <c r="BO54">
+        <v>17075</v>
+      </c>
+      <c r="BP54">
+        <v>8791.6</v>
+      </c>
+      <c r="BQ54">
+        <v>202283.2</v>
+      </c>
     </row>
-    <row r="55" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A55" s="241">
         <v>2554</v>
       </c>
@@ -12062,8 +13217,29 @@
       <c r="BJ55" s="96">
         <v>23011.09</v>
       </c>
+      <c r="BK55">
+        <v>107716.6</v>
+      </c>
+      <c r="BL55">
+        <v>55000</v>
+      </c>
+      <c r="BM55">
+        <v>3000</v>
+      </c>
+      <c r="BN55">
+        <v>10700</v>
+      </c>
+      <c r="BO55">
+        <v>17075</v>
+      </c>
+      <c r="BP55">
+        <v>8791.6</v>
+      </c>
+      <c r="BQ55">
+        <v>202283.2</v>
+      </c>
     </row>
-    <row r="56" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A56" s="241">
         <v>2554</v>
       </c>
@@ -12246,8 +13422,29 @@
       <c r="BJ56" s="96">
         <v>23190.87</v>
       </c>
+      <c r="BK56">
+        <v>107716.6</v>
+      </c>
+      <c r="BL56">
+        <v>55000</v>
+      </c>
+      <c r="BM56">
+        <v>3000</v>
+      </c>
+      <c r="BN56">
+        <v>10700</v>
+      </c>
+      <c r="BO56">
+        <v>17075</v>
+      </c>
+      <c r="BP56">
+        <v>8791.6</v>
+      </c>
+      <c r="BQ56">
+        <v>202283.2</v>
+      </c>
     </row>
-    <row r="57" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A57" s="241">
         <v>2554</v>
       </c>
@@ -12430,8 +13627,29 @@
       <c r="BJ57" s="96">
         <v>24211.27</v>
       </c>
+      <c r="BK57">
+        <v>107716.6</v>
+      </c>
+      <c r="BL57">
+        <v>55000</v>
+      </c>
+      <c r="BM57">
+        <v>3000</v>
+      </c>
+      <c r="BN57">
+        <v>10700</v>
+      </c>
+      <c r="BO57">
+        <v>17075</v>
+      </c>
+      <c r="BP57">
+        <v>8791.6</v>
+      </c>
+      <c r="BQ57">
+        <v>202283.2</v>
+      </c>
     </row>
-    <row r="58" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A58" s="241">
         <v>2554</v>
       </c>
@@ -12614,8 +13832,29 @@
       <c r="BJ58" s="96">
         <v>23996.240000000002</v>
       </c>
+      <c r="BK58">
+        <v>107716.6</v>
+      </c>
+      <c r="BL58">
+        <v>55000</v>
+      </c>
+      <c r="BM58">
+        <v>3000</v>
+      </c>
+      <c r="BN58">
+        <v>10700</v>
+      </c>
+      <c r="BO58">
+        <v>17075</v>
+      </c>
+      <c r="BP58">
+        <v>8791.6</v>
+      </c>
+      <c r="BQ58">
+        <v>202283.2</v>
+      </c>
     </row>
-    <row r="59" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A59" s="241">
         <v>2554</v>
       </c>
@@ -12798,8 +14037,29 @@
       <c r="BJ59" s="96">
         <v>24699.24</v>
       </c>
+      <c r="BK59">
+        <v>107716.6</v>
+      </c>
+      <c r="BL59">
+        <v>55000</v>
+      </c>
+      <c r="BM59">
+        <v>3000</v>
+      </c>
+      <c r="BN59">
+        <v>10700</v>
+      </c>
+      <c r="BO59">
+        <v>17075</v>
+      </c>
+      <c r="BP59">
+        <v>8791.6</v>
+      </c>
+      <c r="BQ59">
+        <v>202283.2</v>
+      </c>
     </row>
-    <row r="60" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A60" s="241">
         <v>2554</v>
       </c>
@@ -12982,8 +14242,29 @@
       <c r="BJ60" s="96">
         <v>23791.65</v>
       </c>
+      <c r="BK60">
+        <v>107716.6</v>
+      </c>
+      <c r="BL60">
+        <v>55000</v>
+      </c>
+      <c r="BM60">
+        <v>3000</v>
+      </c>
+      <c r="BN60">
+        <v>10700</v>
+      </c>
+      <c r="BO60">
+        <v>17075</v>
+      </c>
+      <c r="BP60">
+        <v>8791.6</v>
+      </c>
+      <c r="BQ60">
+        <v>202283.2</v>
+      </c>
     </row>
-    <row r="61" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A61" s="241">
         <v>2554</v>
       </c>
@@ -13166,8 +14447,29 @@
       <c r="BJ61" s="96">
         <v>22689.31</v>
       </c>
+      <c r="BK61">
+        <v>107716.6</v>
+      </c>
+      <c r="BL61">
+        <v>55000</v>
+      </c>
+      <c r="BM61">
+        <v>3000</v>
+      </c>
+      <c r="BN61">
+        <v>10700</v>
+      </c>
+      <c r="BO61">
+        <v>17075</v>
+      </c>
+      <c r="BP61">
+        <v>8791.6</v>
+      </c>
+      <c r="BQ61">
+        <v>202283.2</v>
+      </c>
     </row>
-    <row r="62" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A62" s="243">
         <v>2555</v>
       </c>
@@ -13354,8 +14656,29 @@
       <c r="BJ62" s="110">
         <v>17077.66</v>
       </c>
+      <c r="BK62">
+        <v>105041.60000000001</v>
+      </c>
+      <c r="BL62">
+        <v>54600</v>
+      </c>
+      <c r="BM62">
+        <v>3375</v>
+      </c>
+      <c r="BN62">
+        <v>9991.6</v>
+      </c>
+      <c r="BO62">
+        <v>16675</v>
+      </c>
+      <c r="BP62">
+        <v>3475</v>
+      </c>
+      <c r="BQ62">
+        <v>193158.2</v>
+      </c>
     </row>
-    <row r="63" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A63" s="243">
         <v>2555</v>
       </c>
@@ -13542,8 +14865,29 @@
       <c r="BJ63" s="110">
         <v>20305.38</v>
       </c>
+      <c r="BK63">
+        <v>105041.60000000001</v>
+      </c>
+      <c r="BL63">
+        <v>54600</v>
+      </c>
+      <c r="BM63">
+        <v>3375</v>
+      </c>
+      <c r="BN63">
+        <v>9991.6</v>
+      </c>
+      <c r="BO63">
+        <v>16675</v>
+      </c>
+      <c r="BP63">
+        <v>3475</v>
+      </c>
+      <c r="BQ63">
+        <v>193158.2</v>
+      </c>
     </row>
-    <row r="64" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A64" s="243">
         <v>2555</v>
       </c>
@@ -13730,8 +15074,29 @@
       <c r="BJ64" s="110">
         <v>22244.89</v>
       </c>
+      <c r="BK64">
+        <v>105041.60000000001</v>
+      </c>
+      <c r="BL64">
+        <v>54600</v>
+      </c>
+      <c r="BM64">
+        <v>3375</v>
+      </c>
+      <c r="BN64">
+        <v>9991.6</v>
+      </c>
+      <c r="BO64">
+        <v>16675</v>
+      </c>
+      <c r="BP64">
+        <v>3475</v>
+      </c>
+      <c r="BQ64">
+        <v>193158.2</v>
+      </c>
     </row>
-    <row r="65" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A65" s="243">
         <v>2555</v>
       </c>
@@ -13918,8 +15283,29 @@
       <c r="BJ65" s="110">
         <v>17707.150000000001</v>
       </c>
+      <c r="BK65">
+        <v>105041.60000000001</v>
+      </c>
+      <c r="BL65">
+        <v>54600</v>
+      </c>
+      <c r="BM65">
+        <v>3375</v>
+      </c>
+      <c r="BN65">
+        <v>9991.6</v>
+      </c>
+      <c r="BO65">
+        <v>16675</v>
+      </c>
+      <c r="BP65">
+        <v>3475</v>
+      </c>
+      <c r="BQ65">
+        <v>193158.2</v>
+      </c>
     </row>
-    <row r="66" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A66" s="243">
         <v>2555</v>
       </c>
@@ -14106,8 +15492,29 @@
       <c r="BJ66" s="110">
         <v>23475.77</v>
       </c>
+      <c r="BK66">
+        <v>105041.60000000001</v>
+      </c>
+      <c r="BL66">
+        <v>54600</v>
+      </c>
+      <c r="BM66">
+        <v>3375</v>
+      </c>
+      <c r="BN66">
+        <v>9991.6</v>
+      </c>
+      <c r="BO66">
+        <v>16675</v>
+      </c>
+      <c r="BP66">
+        <v>3475</v>
+      </c>
+      <c r="BQ66">
+        <v>193158.2</v>
+      </c>
     </row>
-    <row r="67" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A67" s="243">
         <v>2555</v>
       </c>
@@ -14294,8 +15701,29 @@
       <c r="BJ67" s="110">
         <v>23084.38</v>
       </c>
+      <c r="BK67">
+        <v>105041.60000000001</v>
+      </c>
+      <c r="BL67">
+        <v>54600</v>
+      </c>
+      <c r="BM67">
+        <v>3375</v>
+      </c>
+      <c r="BN67">
+        <v>9991.6</v>
+      </c>
+      <c r="BO67">
+        <v>16675</v>
+      </c>
+      <c r="BP67">
+        <v>3475</v>
+      </c>
+      <c r="BQ67">
+        <v>193158.2</v>
+      </c>
     </row>
-    <row r="68" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A68" s="243">
         <v>2555</v>
       </c>
@@ -14482,8 +15910,29 @@
       <c r="BJ68" s="110">
         <v>24169.5</v>
       </c>
+      <c r="BK68">
+        <v>105041.60000000001</v>
+      </c>
+      <c r="BL68">
+        <v>54600</v>
+      </c>
+      <c r="BM68">
+        <v>3375</v>
+      </c>
+      <c r="BN68">
+        <v>9991.6</v>
+      </c>
+      <c r="BO68">
+        <v>16675</v>
+      </c>
+      <c r="BP68">
+        <v>3475</v>
+      </c>
+      <c r="BQ68">
+        <v>193158.2</v>
+      </c>
     </row>
-    <row r="69" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A69" s="243">
         <v>2555</v>
       </c>
@@ -14670,8 +16119,29 @@
       <c r="BJ69" s="110">
         <v>23388.67</v>
       </c>
+      <c r="BK69">
+        <v>105041.60000000001</v>
+      </c>
+      <c r="BL69">
+        <v>54600</v>
+      </c>
+      <c r="BM69">
+        <v>3375</v>
+      </c>
+      <c r="BN69">
+        <v>9991.6</v>
+      </c>
+      <c r="BO69">
+        <v>16675</v>
+      </c>
+      <c r="BP69">
+        <v>3475</v>
+      </c>
+      <c r="BQ69">
+        <v>193158.2</v>
+      </c>
     </row>
-    <row r="70" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A70" s="243">
         <v>2555</v>
       </c>
@@ -14858,8 +16328,29 @@
       <c r="BJ70" s="110">
         <v>23321.55</v>
       </c>
+      <c r="BK70">
+        <v>105041.60000000001</v>
+      </c>
+      <c r="BL70">
+        <v>54600</v>
+      </c>
+      <c r="BM70">
+        <v>3375</v>
+      </c>
+      <c r="BN70">
+        <v>9991.6</v>
+      </c>
+      <c r="BO70">
+        <v>16675</v>
+      </c>
+      <c r="BP70">
+        <v>3475</v>
+      </c>
+      <c r="BQ70">
+        <v>193158.2</v>
+      </c>
     </row>
-    <row r="71" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A71" s="243">
         <v>2555</v>
       </c>
@@ -15046,8 +16537,29 @@
       <c r="BJ71" s="110">
         <v>23708.3</v>
       </c>
+      <c r="BK71">
+        <v>105041.60000000001</v>
+      </c>
+      <c r="BL71">
+        <v>54600</v>
+      </c>
+      <c r="BM71">
+        <v>3375</v>
+      </c>
+      <c r="BN71">
+        <v>9991.6</v>
+      </c>
+      <c r="BO71">
+        <v>16675</v>
+      </c>
+      <c r="BP71">
+        <v>3475</v>
+      </c>
+      <c r="BQ71">
+        <v>193158.2</v>
+      </c>
     </row>
-    <row r="72" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A72" s="243">
         <v>2555</v>
       </c>
@@ -15234,8 +16746,29 @@
       <c r="BJ72" s="110">
         <v>24621.98</v>
       </c>
+      <c r="BK72">
+        <v>105041.60000000001</v>
+      </c>
+      <c r="BL72">
+        <v>54600</v>
+      </c>
+      <c r="BM72">
+        <v>3375</v>
+      </c>
+      <c r="BN72">
+        <v>9991.6</v>
+      </c>
+      <c r="BO72">
+        <v>16675</v>
+      </c>
+      <c r="BP72">
+        <v>3475</v>
+      </c>
+      <c r="BQ72">
+        <v>193158.2</v>
+      </c>
     </row>
-    <row r="73" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A73" s="243">
         <v>2555</v>
       </c>
@@ -15422,8 +16955,29 @@
       <c r="BJ73" s="110">
         <v>21313.31</v>
       </c>
+      <c r="BK73">
+        <v>105041.60000000001</v>
+      </c>
+      <c r="BL73">
+        <v>54600</v>
+      </c>
+      <c r="BM73">
+        <v>3375</v>
+      </c>
+      <c r="BN73">
+        <v>9991.6</v>
+      </c>
+      <c r="BO73">
+        <v>16675</v>
+      </c>
+      <c r="BP73">
+        <v>3475</v>
+      </c>
+      <c r="BQ73">
+        <v>193158.2</v>
+      </c>
     </row>
-    <row r="74" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A74" s="245">
         <v>2556</v>
       </c>
@@ -15610,8 +17164,29 @@
       <c r="BJ74" s="127">
         <v>18907.599999999999</v>
       </c>
+      <c r="BK74">
+        <v>108033.3</v>
+      </c>
+      <c r="BL74">
+        <v>30558.3</v>
+      </c>
+      <c r="BM74">
+        <v>2608.3000000000002</v>
+      </c>
+      <c r="BN74">
+        <v>9750</v>
+      </c>
+      <c r="BO74">
+        <v>19741.599999999999</v>
+      </c>
+      <c r="BP74">
+        <v>10641.6</v>
+      </c>
+      <c r="BQ74">
+        <v>181333.1</v>
+      </c>
     </row>
-    <row r="75" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A75" s="245">
         <v>2556</v>
       </c>
@@ -15798,8 +17373,29 @@
       <c r="BJ75" s="127">
         <v>17797.45</v>
       </c>
+      <c r="BK75">
+        <v>108033.3</v>
+      </c>
+      <c r="BL75">
+        <v>30558.3</v>
+      </c>
+      <c r="BM75">
+        <v>2608.3000000000002</v>
+      </c>
+      <c r="BN75">
+        <v>9750</v>
+      </c>
+      <c r="BO75">
+        <v>19741.599999999999</v>
+      </c>
+      <c r="BP75">
+        <v>10641.6</v>
+      </c>
+      <c r="BQ75">
+        <v>181333.1</v>
+      </c>
     </row>
-    <row r="76" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A76" s="245">
         <v>2556</v>
       </c>
@@ -15986,8 +17582,29 @@
       <c r="BJ76" s="127">
         <v>19744.669999999998</v>
       </c>
+      <c r="BK76">
+        <v>108033.3</v>
+      </c>
+      <c r="BL76">
+        <v>30558.3</v>
+      </c>
+      <c r="BM76">
+        <v>2608.3000000000002</v>
+      </c>
+      <c r="BN76">
+        <v>9750</v>
+      </c>
+      <c r="BO76">
+        <v>19741.599999999999</v>
+      </c>
+      <c r="BP76">
+        <v>10641.6</v>
+      </c>
+      <c r="BQ76">
+        <v>181333.1</v>
+      </c>
     </row>
-    <row r="77" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A77" s="245">
         <v>2556</v>
       </c>
@@ -16174,8 +17791,29 @@
       <c r="BJ77" s="127">
         <v>16578.63</v>
       </c>
+      <c r="BK77">
+        <v>108033.3</v>
+      </c>
+      <c r="BL77">
+        <v>30558.3</v>
+      </c>
+      <c r="BM77">
+        <v>2608.3000000000002</v>
+      </c>
+      <c r="BN77">
+        <v>9750</v>
+      </c>
+      <c r="BO77">
+        <v>19741.599999999999</v>
+      </c>
+      <c r="BP77">
+        <v>10641.6</v>
+      </c>
+      <c r="BQ77">
+        <v>181333.1</v>
+      </c>
     </row>
-    <row r="78" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A78" s="245">
         <v>2556</v>
       </c>
@@ -16362,8 +18000,29 @@
       <c r="BJ78" s="127">
         <v>18744.78</v>
       </c>
+      <c r="BK78">
+        <v>108033.3</v>
+      </c>
+      <c r="BL78">
+        <v>30558.3</v>
+      </c>
+      <c r="BM78">
+        <v>2608.3000000000002</v>
+      </c>
+      <c r="BN78">
+        <v>9750</v>
+      </c>
+      <c r="BO78">
+        <v>19741.599999999999</v>
+      </c>
+      <c r="BP78">
+        <v>10641.6</v>
+      </c>
+      <c r="BQ78">
+        <v>181333.1</v>
+      </c>
     </row>
-    <row r="79" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A79" s="245">
         <v>2556</v>
       </c>
@@ -16550,8 +18209,29 @@
       <c r="BJ79" s="127">
         <v>17906.89</v>
       </c>
+      <c r="BK79">
+        <v>108033.3</v>
+      </c>
+      <c r="BL79">
+        <v>30558.3</v>
+      </c>
+      <c r="BM79">
+        <v>2608.3000000000002</v>
+      </c>
+      <c r="BN79">
+        <v>9750</v>
+      </c>
+      <c r="BO79">
+        <v>19741.599999999999</v>
+      </c>
+      <c r="BP79">
+        <v>10641.6</v>
+      </c>
+      <c r="BQ79">
+        <v>181333.1</v>
+      </c>
     </row>
-    <row r="80" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A80" s="245">
         <v>2556</v>
       </c>
@@ -16738,8 +18418,29 @@
       <c r="BJ80" s="135">
         <v>0</v>
       </c>
+      <c r="BK80">
+        <v>108033.3</v>
+      </c>
+      <c r="BL80">
+        <v>30558.3</v>
+      </c>
+      <c r="BM80">
+        <v>2608.3000000000002</v>
+      </c>
+      <c r="BN80">
+        <v>9750</v>
+      </c>
+      <c r="BO80">
+        <v>19741.599999999999</v>
+      </c>
+      <c r="BP80">
+        <v>10641.6</v>
+      </c>
+      <c r="BQ80">
+        <v>181333.1</v>
+      </c>
     </row>
-    <row r="81" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A81" s="245">
         <v>2556</v>
       </c>
@@ -16926,8 +18627,29 @@
       <c r="BJ81" s="127">
         <v>19421.3</v>
       </c>
+      <c r="BK81">
+        <v>108033.3</v>
+      </c>
+      <c r="BL81">
+        <v>30558.3</v>
+      </c>
+      <c r="BM81">
+        <v>2608.3000000000002</v>
+      </c>
+      <c r="BN81">
+        <v>9750</v>
+      </c>
+      <c r="BO81">
+        <v>19741.599999999999</v>
+      </c>
+      <c r="BP81">
+        <v>10641.6</v>
+      </c>
+      <c r="BQ81">
+        <v>181333.1</v>
+      </c>
     </row>
-    <row r="82" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A82" s="245">
         <v>2556</v>
       </c>
@@ -17114,8 +18836,29 @@
       <c r="BJ82" s="127">
         <v>19887.89</v>
       </c>
+      <c r="BK82">
+        <v>108033.3</v>
+      </c>
+      <c r="BL82">
+        <v>30558.3</v>
+      </c>
+      <c r="BM82">
+        <v>2608.3000000000002</v>
+      </c>
+      <c r="BN82">
+        <v>9750</v>
+      </c>
+      <c r="BO82">
+        <v>19741.599999999999</v>
+      </c>
+      <c r="BP82">
+        <v>10641.6</v>
+      </c>
+      <c r="BQ82">
+        <v>181333.1</v>
+      </c>
     </row>
-    <row r="83" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A83" s="245">
         <v>2556</v>
       </c>
@@ -17302,8 +19045,29 @@
       <c r="BJ83" s="127">
         <v>21475.279999999999</v>
       </c>
+      <c r="BK83">
+        <v>108033.3</v>
+      </c>
+      <c r="BL83">
+        <v>30558.3</v>
+      </c>
+      <c r="BM83">
+        <v>2608.3000000000002</v>
+      </c>
+      <c r="BN83">
+        <v>9750</v>
+      </c>
+      <c r="BO83">
+        <v>19741.599999999999</v>
+      </c>
+      <c r="BP83">
+        <v>10641.6</v>
+      </c>
+      <c r="BQ83">
+        <v>181333.1</v>
+      </c>
     </row>
-    <row r="84" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A84" s="245">
         <v>2556</v>
       </c>
@@ -17490,8 +19254,29 @@
       <c r="BJ84" s="127">
         <v>21441.81</v>
       </c>
+      <c r="BK84">
+        <v>108033.3</v>
+      </c>
+      <c r="BL84">
+        <v>30558.3</v>
+      </c>
+      <c r="BM84">
+        <v>2608.3000000000002</v>
+      </c>
+      <c r="BN84">
+        <v>9750</v>
+      </c>
+      <c r="BO84">
+        <v>19741.599999999999</v>
+      </c>
+      <c r="BP84">
+        <v>10641.6</v>
+      </c>
+      <c r="BQ84">
+        <v>181333.1</v>
+      </c>
     </row>
-    <row r="85" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A85" s="245">
         <v>2556</v>
       </c>
@@ -17678,8 +19463,29 @@
       <c r="BJ85" s="143">
         <v>17442.05</v>
       </c>
+      <c r="BK85">
+        <v>108033.3</v>
+      </c>
+      <c r="BL85">
+        <v>30558.3</v>
+      </c>
+      <c r="BM85">
+        <v>2608.3000000000002</v>
+      </c>
+      <c r="BN85">
+        <v>9750</v>
+      </c>
+      <c r="BO85">
+        <v>19741.599999999999</v>
+      </c>
+      <c r="BP85">
+        <v>10641.6</v>
+      </c>
+      <c r="BQ85">
+        <v>181333.1</v>
+      </c>
     </row>
-    <row r="86" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A86" s="247">
         <v>2557</v>
       </c>
@@ -17866,8 +19672,29 @@
       <c r="BJ86" s="154">
         <v>18100.84</v>
       </c>
+      <c r="BK86">
+        <v>104525</v>
+      </c>
+      <c r="BL86">
+        <v>26691.599999999999</v>
+      </c>
+      <c r="BM86">
+        <v>2366.6</v>
+      </c>
+      <c r="BN86">
+        <v>8408.2999999999993</v>
+      </c>
+      <c r="BO86">
+        <v>16816.599999999999</v>
+      </c>
+      <c r="BP86">
+        <v>5433.3</v>
+      </c>
+      <c r="BQ86">
+        <v>164241.4</v>
+      </c>
     </row>
-    <row r="87" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A87" s="247">
         <v>2557</v>
       </c>
@@ -18054,8 +19881,29 @@
       <c r="BJ87" s="154">
         <v>17085.73</v>
       </c>
+      <c r="BK87">
+        <v>104525</v>
+      </c>
+      <c r="BL87">
+        <v>26691.599999999999</v>
+      </c>
+      <c r="BM87">
+        <v>2366.6</v>
+      </c>
+      <c r="BN87">
+        <v>8408.2999999999993</v>
+      </c>
+      <c r="BO87">
+        <v>16816.599999999999</v>
+      </c>
+      <c r="BP87">
+        <v>5433.3</v>
+      </c>
+      <c r="BQ87">
+        <v>164241.4</v>
+      </c>
     </row>
-    <row r="88" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A88" s="247">
         <v>2557</v>
       </c>
@@ -18242,8 +20090,29 @@
       <c r="BJ88" s="154">
         <v>18957.07</v>
       </c>
+      <c r="BK88">
+        <v>104525</v>
+      </c>
+      <c r="BL88">
+        <v>26691.599999999999</v>
+      </c>
+      <c r="BM88">
+        <v>2366.6</v>
+      </c>
+      <c r="BN88">
+        <v>8408.2999999999993</v>
+      </c>
+      <c r="BO88">
+        <v>16816.599999999999</v>
+      </c>
+      <c r="BP88">
+        <v>5433.3</v>
+      </c>
+      <c r="BQ88">
+        <v>164241.4</v>
+      </c>
     </row>
-    <row r="89" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A89" s="247">
         <v>2557</v>
       </c>
@@ -18430,8 +20299,29 @@
       <c r="BJ89" s="154">
         <v>16913.61</v>
       </c>
+      <c r="BK89">
+        <v>104525</v>
+      </c>
+      <c r="BL89">
+        <v>26691.599999999999</v>
+      </c>
+      <c r="BM89">
+        <v>2366.6</v>
+      </c>
+      <c r="BN89">
+        <v>8408.2999999999993</v>
+      </c>
+      <c r="BO89">
+        <v>16816.599999999999</v>
+      </c>
+      <c r="BP89">
+        <v>5433.3</v>
+      </c>
+      <c r="BQ89">
+        <v>164241.4</v>
+      </c>
     </row>
-    <row r="90" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A90" s="247">
         <v>2557</v>
       </c>
@@ -18618,8 +20508,29 @@
       <c r="BJ90" s="154">
         <v>18141.39</v>
       </c>
+      <c r="BK90">
+        <v>104525</v>
+      </c>
+      <c r="BL90">
+        <v>26691.599999999999</v>
+      </c>
+      <c r="BM90">
+        <v>2366.6</v>
+      </c>
+      <c r="BN90">
+        <v>8408.2999999999993</v>
+      </c>
+      <c r="BO90">
+        <v>16816.599999999999</v>
+      </c>
+      <c r="BP90">
+        <v>5433.3</v>
+      </c>
+      <c r="BQ90">
+        <v>164241.4</v>
+      </c>
     </row>
-    <row r="91" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A91" s="247">
         <v>2557</v>
       </c>
@@ -18806,8 +20717,29 @@
       <c r="BJ91" s="154">
         <v>18427.490000000002</v>
       </c>
+      <c r="BK91">
+        <v>104525</v>
+      </c>
+      <c r="BL91">
+        <v>26691.599999999999</v>
+      </c>
+      <c r="BM91">
+        <v>2366.6</v>
+      </c>
+      <c r="BN91">
+        <v>8408.2999999999993</v>
+      </c>
+      <c r="BO91">
+        <v>16816.599999999999</v>
+      </c>
+      <c r="BP91">
+        <v>5433.3</v>
+      </c>
+      <c r="BQ91">
+        <v>164241.4</v>
+      </c>
     </row>
-    <row r="92" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A92" s="247">
         <v>2557</v>
       </c>
@@ -18994,8 +20926,29 @@
       <c r="BJ92" s="154">
         <v>19888.77</v>
       </c>
+      <c r="BK92">
+        <v>104525</v>
+      </c>
+      <c r="BL92">
+        <v>26691.599999999999</v>
+      </c>
+      <c r="BM92">
+        <v>2366.6</v>
+      </c>
+      <c r="BN92">
+        <v>8408.2999999999993</v>
+      </c>
+      <c r="BO92">
+        <v>16816.599999999999</v>
+      </c>
+      <c r="BP92">
+        <v>5433.3</v>
+      </c>
+      <c r="BQ92">
+        <v>164241.4</v>
+      </c>
     </row>
-    <row r="93" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A93" s="247">
         <v>2557</v>
       </c>
@@ -19182,8 +21135,29 @@
       <c r="BJ93" s="154">
         <v>18223.68</v>
       </c>
+      <c r="BK93">
+        <v>104525</v>
+      </c>
+      <c r="BL93">
+        <v>26691.599999999999</v>
+      </c>
+      <c r="BM93">
+        <v>2366.6</v>
+      </c>
+      <c r="BN93">
+        <v>8408.2999999999993</v>
+      </c>
+      <c r="BO93">
+        <v>16816.599999999999</v>
+      </c>
+      <c r="BP93">
+        <v>5433.3</v>
+      </c>
+      <c r="BQ93">
+        <v>164241.4</v>
+      </c>
     </row>
-    <row r="94" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A94" s="247">
         <v>2557</v>
       </c>
@@ -19370,8 +21344,29 @@
       <c r="BJ94" s="154">
         <v>19853.53</v>
       </c>
+      <c r="BK94">
+        <v>104525</v>
+      </c>
+      <c r="BL94">
+        <v>26691.599999999999</v>
+      </c>
+      <c r="BM94">
+        <v>2366.6</v>
+      </c>
+      <c r="BN94">
+        <v>8408.2999999999993</v>
+      </c>
+      <c r="BO94">
+        <v>16816.599999999999</v>
+      </c>
+      <c r="BP94">
+        <v>5433.3</v>
+      </c>
+      <c r="BQ94">
+        <v>164241.4</v>
+      </c>
     </row>
-    <row r="95" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A95" s="247">
         <v>2557</v>
       </c>
@@ -19558,8 +21553,29 @@
       <c r="BJ95" s="154">
         <v>23204.77</v>
       </c>
+      <c r="BK95">
+        <v>104525</v>
+      </c>
+      <c r="BL95">
+        <v>26691.599999999999</v>
+      </c>
+      <c r="BM95">
+        <v>2366.6</v>
+      </c>
+      <c r="BN95">
+        <v>8408.2999999999993</v>
+      </c>
+      <c r="BO95">
+        <v>16816.599999999999</v>
+      </c>
+      <c r="BP95">
+        <v>5433.3</v>
+      </c>
+      <c r="BQ95">
+        <v>164241.4</v>
+      </c>
     </row>
-    <row r="96" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A96" s="247">
         <v>2557</v>
       </c>
@@ -19746,8 +21762,29 @@
       <c r="BJ96" s="154">
         <v>20410.349999999999</v>
       </c>
+      <c r="BK96">
+        <v>104525</v>
+      </c>
+      <c r="BL96">
+        <v>26691.599999999999</v>
+      </c>
+      <c r="BM96">
+        <v>2366.6</v>
+      </c>
+      <c r="BN96">
+        <v>8408.2999999999993</v>
+      </c>
+      <c r="BO96">
+        <v>16816.599999999999</v>
+      </c>
+      <c r="BP96">
+        <v>5433.3</v>
+      </c>
+      <c r="BQ96">
+        <v>164241.4</v>
+      </c>
     </row>
-    <row r="97" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A97" s="247">
         <v>2557</v>
       </c>
@@ -19934,8 +21971,29 @@
       <c r="BJ97" s="154">
         <v>18653.27</v>
       </c>
+      <c r="BK97">
+        <v>104525</v>
+      </c>
+      <c r="BL97">
+        <v>26691.599999999999</v>
+      </c>
+      <c r="BM97">
+        <v>2366.6</v>
+      </c>
+      <c r="BN97">
+        <v>8408.2999999999993</v>
+      </c>
+      <c r="BO97">
+        <v>16816.599999999999</v>
+      </c>
+      <c r="BP97">
+        <v>5433.3</v>
+      </c>
+      <c r="BQ97">
+        <v>164241.4</v>
+      </c>
     </row>
-    <row r="98" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A98" s="249">
         <v>2558</v>
       </c>
@@ -20122,8 +22180,29 @@
       <c r="BJ98" s="165">
         <v>16893.82</v>
       </c>
+      <c r="BK98">
+        <v>91158.3</v>
+      </c>
+      <c r="BL98">
+        <v>27200</v>
+      </c>
+      <c r="BM98">
+        <v>2241.6</v>
+      </c>
+      <c r="BN98">
+        <v>7583.3</v>
+      </c>
+      <c r="BO98">
+        <v>17600</v>
+      </c>
+      <c r="BP98">
+        <v>6383.3</v>
+      </c>
+      <c r="BQ98">
+        <v>152166.5</v>
+      </c>
     </row>
-    <row r="99" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A99" s="249">
         <v>2558</v>
       </c>
@@ -20310,8 +22389,29 @@
       <c r="BJ99" s="165">
         <v>14994.79</v>
       </c>
+      <c r="BK99">
+        <v>91158.3</v>
+      </c>
+      <c r="BL99">
+        <v>27200</v>
+      </c>
+      <c r="BM99">
+        <v>2241.6</v>
+      </c>
+      <c r="BN99">
+        <v>7583.3</v>
+      </c>
+      <c r="BO99">
+        <v>17600</v>
+      </c>
+      <c r="BP99">
+        <v>6383.3</v>
+      </c>
+      <c r="BQ99">
+        <v>152166.5</v>
+      </c>
     </row>
-    <row r="100" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A100" s="249">
         <v>2558</v>
       </c>
@@ -20498,8 +22598,29 @@
       <c r="BJ100" s="165">
         <v>17304.37</v>
       </c>
+      <c r="BK100">
+        <v>91158.3</v>
+      </c>
+      <c r="BL100">
+        <v>27200</v>
+      </c>
+      <c r="BM100">
+        <v>2241.6</v>
+      </c>
+      <c r="BN100">
+        <v>7583.3</v>
+      </c>
+      <c r="BO100">
+        <v>17600</v>
+      </c>
+      <c r="BP100">
+        <v>6383.3</v>
+      </c>
+      <c r="BQ100">
+        <v>152166.5</v>
+      </c>
     </row>
-    <row r="101" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A101" s="249">
         <v>2558</v>
       </c>
@@ -20686,8 +22807,29 @@
       <c r="BJ101" s="165">
         <v>15311.86</v>
       </c>
+      <c r="BK101">
+        <v>91158.3</v>
+      </c>
+      <c r="BL101">
+        <v>27200</v>
+      </c>
+      <c r="BM101">
+        <v>2241.6</v>
+      </c>
+      <c r="BN101">
+        <v>7583.3</v>
+      </c>
+      <c r="BO101">
+        <v>17600</v>
+      </c>
+      <c r="BP101">
+        <v>6383.3</v>
+      </c>
+      <c r="BQ101">
+        <v>152166.5</v>
+      </c>
     </row>
-    <row r="102" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A102" s="249">
         <v>2558</v>
       </c>
@@ -20874,8 +23016,29 @@
       <c r="BJ102" s="165">
         <v>16320.06</v>
       </c>
+      <c r="BK102">
+        <v>91158.3</v>
+      </c>
+      <c r="BL102">
+        <v>27200</v>
+      </c>
+      <c r="BM102">
+        <v>2241.6</v>
+      </c>
+      <c r="BN102">
+        <v>7583.3</v>
+      </c>
+      <c r="BO102">
+        <v>17600</v>
+      </c>
+      <c r="BP102">
+        <v>6383.3</v>
+      </c>
+      <c r="BQ102">
+        <v>152166.5</v>
+      </c>
     </row>
-    <row r="103" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A103" s="249">
         <v>2558</v>
       </c>
@@ -21062,8 +23225,29 @@
       <c r="BJ103" s="165">
         <v>16867.64</v>
       </c>
+      <c r="BK103">
+        <v>91158.3</v>
+      </c>
+      <c r="BL103">
+        <v>27200</v>
+      </c>
+      <c r="BM103">
+        <v>2241.6</v>
+      </c>
+      <c r="BN103">
+        <v>7583.3</v>
+      </c>
+      <c r="BO103">
+        <v>17600</v>
+      </c>
+      <c r="BP103">
+        <v>6383.3</v>
+      </c>
+      <c r="BQ103">
+        <v>152166.5</v>
+      </c>
     </row>
-    <row r="104" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A104" s="249">
         <v>2558</v>
       </c>
@@ -21250,8 +23434,29 @@
       <c r="BJ104" s="165">
         <v>17145.830000000002</v>
       </c>
+      <c r="BK104">
+        <v>91158.3</v>
+      </c>
+      <c r="BL104">
+        <v>27200</v>
+      </c>
+      <c r="BM104">
+        <v>2241.6</v>
+      </c>
+      <c r="BN104">
+        <v>7583.3</v>
+      </c>
+      <c r="BO104">
+        <v>17600</v>
+      </c>
+      <c r="BP104">
+        <v>6383.3</v>
+      </c>
+      <c r="BQ104">
+        <v>152166.5</v>
+      </c>
     </row>
-    <row r="105" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A105" s="249">
         <v>2558</v>
       </c>
@@ -21438,8 +23643,29 @@
       <c r="BJ105" s="165">
         <v>17100.71</v>
       </c>
+      <c r="BK105">
+        <v>91158.3</v>
+      </c>
+      <c r="BL105">
+        <v>27200</v>
+      </c>
+      <c r="BM105">
+        <v>2241.6</v>
+      </c>
+      <c r="BN105">
+        <v>7583.3</v>
+      </c>
+      <c r="BO105">
+        <v>17600</v>
+      </c>
+      <c r="BP105">
+        <v>6383.3</v>
+      </c>
+      <c r="BQ105">
+        <v>152166.5</v>
+      </c>
     </row>
-    <row r="106" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A106" s="249">
         <v>2558</v>
       </c>
@@ -21626,8 +23852,29 @@
       <c r="BJ106" s="165">
         <v>18848.080000000002</v>
       </c>
+      <c r="BK106">
+        <v>91158.3</v>
+      </c>
+      <c r="BL106">
+        <v>27200</v>
+      </c>
+      <c r="BM106">
+        <v>2241.6</v>
+      </c>
+      <c r="BN106">
+        <v>7583.3</v>
+      </c>
+      <c r="BO106">
+        <v>17600</v>
+      </c>
+      <c r="BP106">
+        <v>6383.3</v>
+      </c>
+      <c r="BQ106">
+        <v>152166.5</v>
+      </c>
     </row>
-    <row r="107" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A107" s="249">
         <v>2558</v>
       </c>
@@ -21814,8 +24061,29 @@
       <c r="BJ107" s="165">
         <v>19390.88</v>
       </c>
+      <c r="BK107">
+        <v>91158.3</v>
+      </c>
+      <c r="BL107">
+        <v>27200</v>
+      </c>
+      <c r="BM107">
+        <v>2241.6</v>
+      </c>
+      <c r="BN107">
+        <v>7583.3</v>
+      </c>
+      <c r="BO107">
+        <v>17600</v>
+      </c>
+      <c r="BP107">
+        <v>6383.3</v>
+      </c>
+      <c r="BQ107">
+        <v>152166.5</v>
+      </c>
     </row>
-    <row r="108" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A108" s="249">
         <v>2558</v>
       </c>
@@ -22002,8 +24270,29 @@
       <c r="BJ108" s="165">
         <v>18920.3</v>
       </c>
+      <c r="BK108">
+        <v>91158.3</v>
+      </c>
+      <c r="BL108">
+        <v>27200</v>
+      </c>
+      <c r="BM108">
+        <v>2241.6</v>
+      </c>
+      <c r="BN108">
+        <v>7583.3</v>
+      </c>
+      <c r="BO108">
+        <v>17600</v>
+      </c>
+      <c r="BP108">
+        <v>6383.3</v>
+      </c>
+      <c r="BQ108">
+        <v>152166.5</v>
+      </c>
     </row>
-    <row r="109" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A109" s="249">
         <v>2558</v>
       </c>
@@ -22190,8 +24479,29 @@
       <c r="BJ109" s="165">
         <v>19050.240000000002</v>
       </c>
+      <c r="BK109">
+        <v>91158.3</v>
+      </c>
+      <c r="BL109">
+        <v>27200</v>
+      </c>
+      <c r="BM109">
+        <v>2241.6</v>
+      </c>
+      <c r="BN109">
+        <v>7583.3</v>
+      </c>
+      <c r="BO109">
+        <v>17600</v>
+      </c>
+      <c r="BP109">
+        <v>6383.3</v>
+      </c>
+      <c r="BQ109">
+        <v>152166.5</v>
+      </c>
     </row>
-    <row r="110" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A110" s="251">
         <v>2559</v>
       </c>
@@ -22378,8 +24688,29 @@
       <c r="BJ110" s="176">
         <v>15205.95</v>
       </c>
+      <c r="BK110">
+        <v>90566.6</v>
+      </c>
+      <c r="BL110">
+        <v>31566.6</v>
+      </c>
+      <c r="BM110">
+        <v>3008.3</v>
+      </c>
+      <c r="BN110">
+        <v>9083.2999999999993</v>
+      </c>
+      <c r="BO110">
+        <v>14058.3</v>
+      </c>
+      <c r="BP110">
+        <v>5333.3</v>
+      </c>
+      <c r="BQ110">
+        <v>153616.4</v>
+      </c>
     </row>
-    <row r="111" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A111" s="251">
         <v>2559</v>
       </c>
@@ -22566,8 +24897,29 @@
       <c r="BJ111" s="176">
         <v>16133.29</v>
       </c>
+      <c r="BK111">
+        <v>90566.6</v>
+      </c>
+      <c r="BL111">
+        <v>31566.6</v>
+      </c>
+      <c r="BM111">
+        <v>3008.3</v>
+      </c>
+      <c r="BN111">
+        <v>9083.2999999999993</v>
+      </c>
+      <c r="BO111">
+        <v>14058.3</v>
+      </c>
+      <c r="BP111">
+        <v>5333.3</v>
+      </c>
+      <c r="BQ111">
+        <v>153616.4</v>
+      </c>
     </row>
-    <row r="112" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A112" s="251">
         <v>2559</v>
       </c>
@@ -22754,8 +25106,29 @@
       <c r="BJ112" s="176">
         <v>18536.59</v>
       </c>
+      <c r="BK112">
+        <v>90566.6</v>
+      </c>
+      <c r="BL112">
+        <v>31566.6</v>
+      </c>
+      <c r="BM112">
+        <v>3008.3</v>
+      </c>
+      <c r="BN112">
+        <v>9083.2999999999993</v>
+      </c>
+      <c r="BO112">
+        <v>14058.3</v>
+      </c>
+      <c r="BP112">
+        <v>5333.3</v>
+      </c>
+      <c r="BQ112">
+        <v>153616.4</v>
+      </c>
     </row>
-    <row r="113" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A113" s="251">
         <v>2559</v>
       </c>
@@ -22942,8 +25315,29 @@
       <c r="BJ113" s="176">
         <v>15298.45</v>
       </c>
+      <c r="BK113">
+        <v>90566.6</v>
+      </c>
+      <c r="BL113">
+        <v>31566.6</v>
+      </c>
+      <c r="BM113">
+        <v>3008.3</v>
+      </c>
+      <c r="BN113">
+        <v>9083.2999999999993</v>
+      </c>
+      <c r="BO113">
+        <v>14058.3</v>
+      </c>
+      <c r="BP113">
+        <v>5333.3</v>
+      </c>
+      <c r="BQ113">
+        <v>153616.4</v>
+      </c>
     </row>
-    <row r="114" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A114" s="251">
         <v>2559</v>
       </c>
@@ -23130,8 +25524,29 @@
       <c r="BJ114" s="176">
         <v>18775.150000000001</v>
       </c>
+      <c r="BK114">
+        <v>90566.6</v>
+      </c>
+      <c r="BL114">
+        <v>31566.6</v>
+      </c>
+      <c r="BM114">
+        <v>3008.3</v>
+      </c>
+      <c r="BN114">
+        <v>9083.2999999999993</v>
+      </c>
+      <c r="BO114">
+        <v>14058.3</v>
+      </c>
+      <c r="BP114">
+        <v>5333.3</v>
+      </c>
+      <c r="BQ114">
+        <v>153616.4</v>
+      </c>
     </row>
-    <row r="115" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A115" s="251">
         <v>2559</v>
       </c>
@@ -23318,8 +25733,29 @@
       <c r="BJ115" s="176">
         <v>19300.98</v>
       </c>
+      <c r="BK115">
+        <v>90566.6</v>
+      </c>
+      <c r="BL115">
+        <v>31566.6</v>
+      </c>
+      <c r="BM115">
+        <v>3008.3</v>
+      </c>
+      <c r="BN115">
+        <v>9083.2999999999993</v>
+      </c>
+      <c r="BO115">
+        <v>14058.3</v>
+      </c>
+      <c r="BP115">
+        <v>5333.3</v>
+      </c>
+      <c r="BQ115">
+        <v>153616.4</v>
+      </c>
     </row>
-    <row r="116" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A116" s="251">
         <v>2559</v>
       </c>
@@ -23506,8 +25942,29 @@
       <c r="BJ116" s="176">
         <v>18347.43</v>
       </c>
+      <c r="BK116">
+        <v>90566.6</v>
+      </c>
+      <c r="BL116">
+        <v>31566.6</v>
+      </c>
+      <c r="BM116">
+        <v>3008.3</v>
+      </c>
+      <c r="BN116">
+        <v>9083.2999999999993</v>
+      </c>
+      <c r="BO116">
+        <v>14058.3</v>
+      </c>
+      <c r="BP116">
+        <v>5333.3</v>
+      </c>
+      <c r="BQ116">
+        <v>153616.4</v>
+      </c>
     </row>
-    <row r="117" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A117" s="251">
         <v>2559</v>
       </c>
@@ -23694,8 +26151,29 @@
       <c r="BJ117" s="176">
         <v>18225.93</v>
       </c>
+      <c r="BK117">
+        <v>90566.6</v>
+      </c>
+      <c r="BL117">
+        <v>31566.6</v>
+      </c>
+      <c r="BM117">
+        <v>3008.3</v>
+      </c>
+      <c r="BN117">
+        <v>9083.2999999999993</v>
+      </c>
+      <c r="BO117">
+        <v>14058.3</v>
+      </c>
+      <c r="BP117">
+        <v>5333.3</v>
+      </c>
+      <c r="BQ117">
+        <v>153616.4</v>
+      </c>
     </row>
-    <row r="118" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A118" s="251">
         <v>2559</v>
       </c>
@@ -23882,8 +26360,29 @@
       <c r="BJ118" s="176">
         <v>20374.34</v>
       </c>
+      <c r="BK118">
+        <v>90566.6</v>
+      </c>
+      <c r="BL118">
+        <v>31566.6</v>
+      </c>
+      <c r="BM118">
+        <v>3008.3</v>
+      </c>
+      <c r="BN118">
+        <v>9083.2999999999993</v>
+      </c>
+      <c r="BO118">
+        <v>14058.3</v>
+      </c>
+      <c r="BP118">
+        <v>5333.3</v>
+      </c>
+      <c r="BQ118">
+        <v>153616.4</v>
+      </c>
     </row>
-    <row r="119" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A119" s="251">
         <v>2559</v>
       </c>
@@ -24070,8 +26569,29 @@
       <c r="BJ119" s="176">
         <v>20510.2</v>
       </c>
+      <c r="BK119">
+        <v>90566.6</v>
+      </c>
+      <c r="BL119">
+        <v>31566.6</v>
+      </c>
+      <c r="BM119">
+        <v>3008.3</v>
+      </c>
+      <c r="BN119">
+        <v>9083.2999999999993</v>
+      </c>
+      <c r="BO119">
+        <v>14058.3</v>
+      </c>
+      <c r="BP119">
+        <v>5333.3</v>
+      </c>
+      <c r="BQ119">
+        <v>153616.4</v>
+      </c>
     </row>
-    <row r="120" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A120" s="251">
         <v>2559</v>
       </c>
@@ -24258,8 +26778,29 @@
       <c r="BJ120" s="176">
         <v>20712.71</v>
       </c>
+      <c r="BK120">
+        <v>90566.6</v>
+      </c>
+      <c r="BL120">
+        <v>31566.6</v>
+      </c>
+      <c r="BM120">
+        <v>3008.3</v>
+      </c>
+      <c r="BN120">
+        <v>9083.2999999999993</v>
+      </c>
+      <c r="BO120">
+        <v>14058.3</v>
+      </c>
+      <c r="BP120">
+        <v>5333.3</v>
+      </c>
+      <c r="BQ120">
+        <v>153616.4</v>
+      </c>
     </row>
-    <row r="121" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A121" s="251">
         <v>2559</v>
       </c>
@@ -24446,8 +26987,29 @@
       <c r="BJ121" s="176">
         <v>19125.77</v>
       </c>
+      <c r="BK121">
+        <v>90566.6</v>
+      </c>
+      <c r="BL121">
+        <v>31566.6</v>
+      </c>
+      <c r="BM121">
+        <v>3008.3</v>
+      </c>
+      <c r="BN121">
+        <v>9083.2999999999993</v>
+      </c>
+      <c r="BO121">
+        <v>14058.3</v>
+      </c>
+      <c r="BP121">
+        <v>5333.3</v>
+      </c>
+      <c r="BQ121">
+        <v>153616.4</v>
+      </c>
     </row>
-    <row r="122" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A122" s="235">
         <v>2560</v>
       </c>
@@ -24622,8 +27184,29 @@
       <c r="BJ122" s="58">
         <v>15228.71</v>
       </c>
+      <c r="BK122">
+        <v>89350</v>
+      </c>
+      <c r="BL122">
+        <v>33016.6</v>
+      </c>
+      <c r="BM122">
+        <v>2991.6</v>
+      </c>
+      <c r="BN122">
+        <v>8175</v>
+      </c>
+      <c r="BO122">
+        <v>9866.6</v>
+      </c>
+      <c r="BP122">
+        <v>5091.6000000000004</v>
+      </c>
+      <c r="BQ122">
+        <v>148491.4</v>
+      </c>
     </row>
-    <row r="123" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A123" s="235">
         <v>2560</v>
       </c>
@@ -24798,8 +27381,29 @@
       <c r="BJ123" s="58">
         <v>16020.52</v>
       </c>
+      <c r="BK123">
+        <v>89350</v>
+      </c>
+      <c r="BL123">
+        <v>33016.6</v>
+      </c>
+      <c r="BM123">
+        <v>2991.6</v>
+      </c>
+      <c r="BN123">
+        <v>8175</v>
+      </c>
+      <c r="BO123">
+        <v>9866.6</v>
+      </c>
+      <c r="BP123">
+        <v>5091.6000000000004</v>
+      </c>
+      <c r="BQ123">
+        <v>148491.4</v>
+      </c>
     </row>
-    <row r="124" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A124" s="235">
         <v>2560</v>
       </c>
@@ -24974,8 +27578,29 @@
       <c r="BJ124" s="58">
         <v>19017.93</v>
       </c>
+      <c r="BK124">
+        <v>89350</v>
+      </c>
+      <c r="BL124">
+        <v>33016.6</v>
+      </c>
+      <c r="BM124">
+        <v>2991.6</v>
+      </c>
+      <c r="BN124">
+        <v>8175</v>
+      </c>
+      <c r="BO124">
+        <v>9866.6</v>
+      </c>
+      <c r="BP124">
+        <v>5091.6000000000004</v>
+      </c>
+      <c r="BQ124">
+        <v>148491.4</v>
+      </c>
     </row>
-    <row r="125" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A125" s="235">
         <v>2560</v>
       </c>
@@ -25150,8 +27775,29 @@
       <c r="BJ125" s="58">
         <v>13477.68</v>
       </c>
+      <c r="BK125">
+        <v>89350</v>
+      </c>
+      <c r="BL125">
+        <v>33016.6</v>
+      </c>
+      <c r="BM125">
+        <v>2991.6</v>
+      </c>
+      <c r="BN125">
+        <v>8175</v>
+      </c>
+      <c r="BO125">
+        <v>9866.6</v>
+      </c>
+      <c r="BP125">
+        <v>5091.6000000000004</v>
+      </c>
+      <c r="BQ125">
+        <v>148491.4</v>
+      </c>
     </row>
-    <row r="126" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A126" s="235">
         <v>2560</v>
       </c>
@@ -25326,8 +27972,29 @@
       <c r="BJ126" s="58">
         <v>19850.189999999999</v>
       </c>
+      <c r="BK126">
+        <v>89350</v>
+      </c>
+      <c r="BL126">
+        <v>33016.6</v>
+      </c>
+      <c r="BM126">
+        <v>2991.6</v>
+      </c>
+      <c r="BN126">
+        <v>8175</v>
+      </c>
+      <c r="BO126">
+        <v>9866.6</v>
+      </c>
+      <c r="BP126">
+        <v>5091.6000000000004</v>
+      </c>
+      <c r="BQ126">
+        <v>148491.4</v>
+      </c>
     </row>
-    <row r="127" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A127" s="235">
         <v>2560</v>
       </c>
@@ -25502,8 +28169,29 @@
       <c r="BJ127" s="58">
         <v>19722.21</v>
       </c>
+      <c r="BK127">
+        <v>89350</v>
+      </c>
+      <c r="BL127">
+        <v>33016.6</v>
+      </c>
+      <c r="BM127">
+        <v>2991.6</v>
+      </c>
+      <c r="BN127">
+        <v>8175</v>
+      </c>
+      <c r="BO127">
+        <v>9866.6</v>
+      </c>
+      <c r="BP127">
+        <v>5091.6000000000004</v>
+      </c>
+      <c r="BQ127">
+        <v>148491.4</v>
+      </c>
     </row>
-    <row r="128" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A128" s="235">
         <v>2560</v>
       </c>
@@ -25678,8 +28366,29 @@
       <c r="BJ128" s="58">
         <v>18191.5</v>
       </c>
+      <c r="BK128">
+        <v>89350</v>
+      </c>
+      <c r="BL128">
+        <v>33016.6</v>
+      </c>
+      <c r="BM128">
+        <v>2991.6</v>
+      </c>
+      <c r="BN128">
+        <v>8175</v>
+      </c>
+      <c r="BO128">
+        <v>9866.6</v>
+      </c>
+      <c r="BP128">
+        <v>5091.6000000000004</v>
+      </c>
+      <c r="BQ128">
+        <v>148491.4</v>
+      </c>
     </row>
-    <row r="129" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A129" s="235">
         <v>2560</v>
       </c>
@@ -25854,8 +28563,29 @@
       <c r="BJ129" s="58">
         <v>19875.2</v>
       </c>
+      <c r="BK129">
+        <v>89350</v>
+      </c>
+      <c r="BL129">
+        <v>33016.6</v>
+      </c>
+      <c r="BM129">
+        <v>2991.6</v>
+      </c>
+      <c r="BN129">
+        <v>8175</v>
+      </c>
+      <c r="BO129">
+        <v>9866.6</v>
+      </c>
+      <c r="BP129">
+        <v>5091.6000000000004</v>
+      </c>
+      <c r="BQ129">
+        <v>148491.4</v>
+      </c>
     </row>
-    <row r="130" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A130" s="235">
         <v>2560</v>
       </c>
@@ -26030,8 +28760,29 @@
       <c r="BJ130" s="58">
         <v>19466.73</v>
       </c>
+      <c r="BK130">
+        <v>89350</v>
+      </c>
+      <c r="BL130">
+        <v>33016.6</v>
+      </c>
+      <c r="BM130">
+        <v>2991.6</v>
+      </c>
+      <c r="BN130">
+        <v>8175</v>
+      </c>
+      <c r="BO130">
+        <v>9866.6</v>
+      </c>
+      <c r="BP130">
+        <v>5091.6000000000004</v>
+      </c>
+      <c r="BQ130">
+        <v>148491.4</v>
+      </c>
     </row>
-    <row r="131" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A131" s="235">
         <v>2560</v>
       </c>
@@ -26206,8 +28957,29 @@
       <c r="BJ131" s="58">
         <v>19459.77</v>
       </c>
+      <c r="BK131">
+        <v>89350</v>
+      </c>
+      <c r="BL131">
+        <v>33016.6</v>
+      </c>
+      <c r="BM131">
+        <v>2991.6</v>
+      </c>
+      <c r="BN131">
+        <v>8175</v>
+      </c>
+      <c r="BO131">
+        <v>9866.6</v>
+      </c>
+      <c r="BP131">
+        <v>5091.6000000000004</v>
+      </c>
+      <c r="BQ131">
+        <v>148491.4</v>
+      </c>
     </row>
-    <row r="132" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A132" s="235">
         <v>2560</v>
       </c>
@@ -26382,8 +29154,29 @@
       <c r="BJ132" s="58">
         <v>20141.7</v>
       </c>
+      <c r="BK132">
+        <v>89350</v>
+      </c>
+      <c r="BL132">
+        <v>33016.6</v>
+      </c>
+      <c r="BM132">
+        <v>2991.6</v>
+      </c>
+      <c r="BN132">
+        <v>8175</v>
+      </c>
+      <c r="BO132">
+        <v>9866.6</v>
+      </c>
+      <c r="BP132">
+        <v>5091.6000000000004</v>
+      </c>
+      <c r="BQ132">
+        <v>148491.4</v>
+      </c>
     </row>
-    <row r="133" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A133" s="235">
         <v>2560</v>
       </c>
@@ -26558,8 +29351,29 @@
       <c r="BJ133" s="58">
         <v>17995.490000000002</v>
       </c>
+      <c r="BK133">
+        <v>89350</v>
+      </c>
+      <c r="BL133">
+        <v>33016.6</v>
+      </c>
+      <c r="BM133">
+        <v>2991.6</v>
+      </c>
+      <c r="BN133">
+        <v>8175</v>
+      </c>
+      <c r="BO133">
+        <v>9866.6</v>
+      </c>
+      <c r="BP133">
+        <v>5091.6000000000004</v>
+      </c>
+      <c r="BQ133">
+        <v>148491.4</v>
+      </c>
     </row>
-    <row r="134" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A134" s="239">
         <v>2561</v>
       </c>
@@ -26738,8 +29552,29 @@
       <c r="BJ134" s="83">
         <v>17166.28</v>
       </c>
+      <c r="BK134">
+        <v>96400</v>
+      </c>
+      <c r="BL134">
+        <v>35600</v>
+      </c>
+      <c r="BM134">
+        <v>2833.3</v>
+      </c>
+      <c r="BN134">
+        <v>9266.6</v>
+      </c>
+      <c r="BO134">
+        <v>8483.2999999999993</v>
+      </c>
+      <c r="BP134">
+        <v>4833.3</v>
+      </c>
+      <c r="BQ134">
+        <v>157416.5</v>
+      </c>
     </row>
-    <row r="135" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A135" s="239">
         <v>2561</v>
       </c>
@@ -26918,8 +29753,29 @@
       <c r="BJ135" s="83">
         <v>14811.55</v>
       </c>
+      <c r="BK135">
+        <v>96400</v>
+      </c>
+      <c r="BL135">
+        <v>35600</v>
+      </c>
+      <c r="BM135">
+        <v>2833.3</v>
+      </c>
+      <c r="BN135">
+        <v>9266.6</v>
+      </c>
+      <c r="BO135">
+        <v>8483.2999999999993</v>
+      </c>
+      <c r="BP135">
+        <v>4833.3</v>
+      </c>
+      <c r="BQ135">
+        <v>157416.5</v>
+      </c>
     </row>
-    <row r="136" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A136" s="239">
         <v>2561</v>
       </c>
@@ -27098,8 +29954,29 @@
       <c r="BJ136" s="83">
         <v>17629.91</v>
       </c>
+      <c r="BK136">
+        <v>96400</v>
+      </c>
+      <c r="BL136">
+        <v>35600</v>
+      </c>
+      <c r="BM136">
+        <v>2833.3</v>
+      </c>
+      <c r="BN136">
+        <v>9266.6</v>
+      </c>
+      <c r="BO136">
+        <v>8483.2999999999993</v>
+      </c>
+      <c r="BP136">
+        <v>4833.3</v>
+      </c>
+      <c r="BQ136">
+        <v>157416.5</v>
+      </c>
     </row>
-    <row r="137" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A137" s="239">
         <v>2561</v>
       </c>
@@ -27278,8 +30155,29 @@
       <c r="BJ137" s="83">
         <v>14777.07</v>
       </c>
+      <c r="BK137">
+        <v>96400</v>
+      </c>
+      <c r="BL137">
+        <v>35600</v>
+      </c>
+      <c r="BM137">
+        <v>2833.3</v>
+      </c>
+      <c r="BN137">
+        <v>9266.6</v>
+      </c>
+      <c r="BO137">
+        <v>8483.2999999999993</v>
+      </c>
+      <c r="BP137">
+        <v>4833.3</v>
+      </c>
+      <c r="BQ137">
+        <v>157416.5</v>
+      </c>
     </row>
-    <row r="138" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A138" s="239">
         <v>2561</v>
       </c>
@@ -27458,8 +30356,29 @@
       <c r="BJ138" s="83">
         <v>18078.12</v>
       </c>
+      <c r="BK138">
+        <v>96400</v>
+      </c>
+      <c r="BL138">
+        <v>35600</v>
+      </c>
+      <c r="BM138">
+        <v>2833.3</v>
+      </c>
+      <c r="BN138">
+        <v>9266.6</v>
+      </c>
+      <c r="BO138">
+        <v>8483.2999999999993</v>
+      </c>
+      <c r="BP138">
+        <v>4833.3</v>
+      </c>
+      <c r="BQ138">
+        <v>157416.5</v>
+      </c>
     </row>
-    <row r="139" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A139" s="239">
         <v>2561</v>
       </c>
@@ -27638,8 +30557,29 @@
       <c r="BJ139" s="83">
         <v>17604.05</v>
       </c>
+      <c r="BK139">
+        <v>96400</v>
+      </c>
+      <c r="BL139">
+        <v>35600</v>
+      </c>
+      <c r="BM139">
+        <v>2833.3</v>
+      </c>
+      <c r="BN139">
+        <v>9266.6</v>
+      </c>
+      <c r="BO139">
+        <v>8483.2999999999993</v>
+      </c>
+      <c r="BP139">
+        <v>4833.3</v>
+      </c>
+      <c r="BQ139">
+        <v>157416.5</v>
+      </c>
     </row>
-    <row r="140" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A140" s="239">
         <v>2561</v>
       </c>
@@ -27818,8 +30758,29 @@
       <c r="BJ140" s="83">
         <v>17906.900000000001</v>
       </c>
+      <c r="BK140">
+        <v>96400</v>
+      </c>
+      <c r="BL140">
+        <v>35600</v>
+      </c>
+      <c r="BM140">
+        <v>2833.3</v>
+      </c>
+      <c r="BN140">
+        <v>9266.6</v>
+      </c>
+      <c r="BO140">
+        <v>8483.2999999999993</v>
+      </c>
+      <c r="BP140">
+        <v>4833.3</v>
+      </c>
+      <c r="BQ140">
+        <v>157416.5</v>
+      </c>
     </row>
-    <row r="141" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A141" s="239">
         <v>2561</v>
       </c>
@@ -27998,8 +30959,29 @@
       <c r="BJ141" s="83">
         <v>19512.52</v>
       </c>
+      <c r="BK141">
+        <v>96400</v>
+      </c>
+      <c r="BL141">
+        <v>35600</v>
+      </c>
+      <c r="BM141">
+        <v>2833.3</v>
+      </c>
+      <c r="BN141">
+        <v>9266.6</v>
+      </c>
+      <c r="BO141">
+        <v>8483.2999999999993</v>
+      </c>
+      <c r="BP141">
+        <v>4833.3</v>
+      </c>
+      <c r="BQ141">
+        <v>157416.5</v>
+      </c>
     </row>
-    <row r="142" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A142" s="239">
         <v>2561</v>
       </c>
@@ -28178,8 +31160,29 @@
       <c r="BJ142" s="83">
         <v>18046.12</v>
       </c>
+      <c r="BK142">
+        <v>96400</v>
+      </c>
+      <c r="BL142">
+        <v>35600</v>
+      </c>
+      <c r="BM142">
+        <v>2833.3</v>
+      </c>
+      <c r="BN142">
+        <v>9266.6</v>
+      </c>
+      <c r="BO142">
+        <v>8483.2999999999993</v>
+      </c>
+      <c r="BP142">
+        <v>4833.3</v>
+      </c>
+      <c r="BQ142">
+        <v>157416.5</v>
+      </c>
     </row>
-    <row r="143" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A143" s="239">
         <v>2561</v>
       </c>
@@ -28358,8 +31361,29 @@
       <c r="BJ143" s="83">
         <v>19866.91</v>
       </c>
+      <c r="BK143">
+        <v>96400</v>
+      </c>
+      <c r="BL143">
+        <v>35600</v>
+      </c>
+      <c r="BM143">
+        <v>2833.3</v>
+      </c>
+      <c r="BN143">
+        <v>9266.6</v>
+      </c>
+      <c r="BO143">
+        <v>8483.2999999999993</v>
+      </c>
+      <c r="BP143">
+        <v>4833.3</v>
+      </c>
+      <c r="BQ143">
+        <v>157416.5</v>
+      </c>
     </row>
-    <row r="144" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A144" s="239">
         <v>2561</v>
       </c>
@@ -28538,8 +31562,29 @@
       <c r="BJ144" s="83">
         <v>19988.79</v>
       </c>
+      <c r="BK144">
+        <v>96400</v>
+      </c>
+      <c r="BL144">
+        <v>35600</v>
+      </c>
+      <c r="BM144">
+        <v>2833.3</v>
+      </c>
+      <c r="BN144">
+        <v>9266.6</v>
+      </c>
+      <c r="BO144">
+        <v>8483.2999999999993</v>
+      </c>
+      <c r="BP144">
+        <v>4833.3</v>
+      </c>
+      <c r="BQ144">
+        <v>157416.5</v>
+      </c>
     </row>
-    <row r="145" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A145" s="239">
         <v>2561</v>
       </c>
@@ -28718,8 +31763,29 @@
       <c r="BJ145" s="83">
         <v>17648.37</v>
       </c>
+      <c r="BK145">
+        <v>96400</v>
+      </c>
+      <c r="BL145">
+        <v>35600</v>
+      </c>
+      <c r="BM145">
+        <v>2833.3</v>
+      </c>
+      <c r="BN145">
+        <v>9266.6</v>
+      </c>
+      <c r="BO145">
+        <v>8483.2999999999993</v>
+      </c>
+      <c r="BP145">
+        <v>4833.3</v>
+      </c>
+      <c r="BQ145">
+        <v>157416.5</v>
+      </c>
     </row>
-    <row r="146" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A146" s="243">
         <v>2562</v>
       </c>
@@ -28898,8 +31964,29 @@
       <c r="BJ146" s="110">
         <v>16289.75</v>
       </c>
+      <c r="BK146">
+        <v>100308.3</v>
+      </c>
+      <c r="BL146">
+        <v>38500</v>
+      </c>
+      <c r="BM146">
+        <v>4383.3</v>
+      </c>
+      <c r="BN146">
+        <v>8191.6</v>
+      </c>
+      <c r="BO146">
+        <v>10166.6</v>
+      </c>
+      <c r="BP146">
+        <v>716.6</v>
+      </c>
+      <c r="BQ146">
+        <v>162266.4</v>
+      </c>
     </row>
-    <row r="147" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A147" s="243">
         <v>2562</v>
       </c>
@@ -29078,8 +32165,29 @@
       <c r="BJ147" s="110">
         <v>15071.12</v>
       </c>
+      <c r="BK147">
+        <v>100308.3</v>
+      </c>
+      <c r="BL147">
+        <v>38500</v>
+      </c>
+      <c r="BM147">
+        <v>4383.3</v>
+      </c>
+      <c r="BN147">
+        <v>8191.6</v>
+      </c>
+      <c r="BO147">
+        <v>10166.6</v>
+      </c>
+      <c r="BP147">
+        <v>716.6</v>
+      </c>
+      <c r="BQ147">
+        <v>162266.4</v>
+      </c>
     </row>
-    <row r="148" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A148" s="243">
         <v>2562</v>
       </c>
@@ -29258,8 +32366,29 @@
       <c r="BJ148" s="110">
         <v>16802.86</v>
       </c>
+      <c r="BK148">
+        <v>100308.3</v>
+      </c>
+      <c r="BL148">
+        <v>38500</v>
+      </c>
+      <c r="BM148">
+        <v>4383.3</v>
+      </c>
+      <c r="BN148">
+        <v>8191.6</v>
+      </c>
+      <c r="BO148">
+        <v>10166.6</v>
+      </c>
+      <c r="BP148">
+        <v>716.6</v>
+      </c>
+      <c r="BQ148">
+        <v>162266.4</v>
+      </c>
     </row>
-    <row r="149" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A149" s="243">
         <v>2562</v>
       </c>
@@ -29438,8 +32567,29 @@
       <c r="BJ149" s="110">
         <v>15175.4</v>
       </c>
+      <c r="BK149">
+        <v>100308.3</v>
+      </c>
+      <c r="BL149">
+        <v>38500</v>
+      </c>
+      <c r="BM149">
+        <v>4383.3</v>
+      </c>
+      <c r="BN149">
+        <v>8191.6</v>
+      </c>
+      <c r="BO149">
+        <v>10166.6</v>
+      </c>
+      <c r="BP149">
+        <v>716.6</v>
+      </c>
+      <c r="BQ149">
+        <v>162266.4</v>
+      </c>
     </row>
-    <row r="150" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A150" s="243">
         <v>2562</v>
       </c>
@@ -29618,8 +32768,29 @@
       <c r="BJ150" s="110">
         <v>17662.03</v>
       </c>
+      <c r="BK150">
+        <v>100308.3</v>
+      </c>
+      <c r="BL150">
+        <v>38500</v>
+      </c>
+      <c r="BM150">
+        <v>4383.3</v>
+      </c>
+      <c r="BN150">
+        <v>8191.6</v>
+      </c>
+      <c r="BO150">
+        <v>10166.6</v>
+      </c>
+      <c r="BP150">
+        <v>716.6</v>
+      </c>
+      <c r="BQ150">
+        <v>162266.4</v>
+      </c>
     </row>
-    <row r="151" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A151" s="243">
         <v>2562</v>
       </c>
@@ -29798,8 +32969,29 @@
       <c r="BJ151" s="110">
         <v>16080.92</v>
       </c>
+      <c r="BK151">
+        <v>100308.3</v>
+      </c>
+      <c r="BL151">
+        <v>38500</v>
+      </c>
+      <c r="BM151">
+        <v>4383.3</v>
+      </c>
+      <c r="BN151">
+        <v>8191.6</v>
+      </c>
+      <c r="BO151">
+        <v>10166.6</v>
+      </c>
+      <c r="BP151">
+        <v>716.6</v>
+      </c>
+      <c r="BQ151">
+        <v>162266.4</v>
+      </c>
     </row>
-    <row r="152" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A152" s="243">
         <v>2562</v>
       </c>
@@ -29978,8 +33170,29 @@
       <c r="BJ152" s="110">
         <v>16607.72</v>
       </c>
+      <c r="BK152">
+        <v>100308.3</v>
+      </c>
+      <c r="BL152">
+        <v>38500</v>
+      </c>
+      <c r="BM152">
+        <v>4383.3</v>
+      </c>
+      <c r="BN152">
+        <v>8191.6</v>
+      </c>
+      <c r="BO152">
+        <v>10166.6</v>
+      </c>
+      <c r="BP152">
+        <v>716.6</v>
+      </c>
+      <c r="BQ152">
+        <v>162266.4</v>
+      </c>
     </row>
-    <row r="153" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A153" s="243">
         <v>2562</v>
       </c>
@@ -30158,8 +33371,29 @@
       <c r="BJ153" s="110">
         <v>16471.13</v>
       </c>
+      <c r="BK153">
+        <v>100308.3</v>
+      </c>
+      <c r="BL153">
+        <v>38500</v>
+      </c>
+      <c r="BM153">
+        <v>4383.3</v>
+      </c>
+      <c r="BN153">
+        <v>8191.6</v>
+      </c>
+      <c r="BO153">
+        <v>10166.6</v>
+      </c>
+      <c r="BP153">
+        <v>716.6</v>
+      </c>
+      <c r="BQ153">
+        <v>162266.4</v>
+      </c>
     </row>
-    <row r="154" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A154" s="243">
         <v>2562</v>
       </c>
@@ -30338,8 +33572,29 @@
       <c r="BJ154" s="110">
         <v>16963.400000000001</v>
       </c>
+      <c r="BK154">
+        <v>100308.3</v>
+      </c>
+      <c r="BL154">
+        <v>38500</v>
+      </c>
+      <c r="BM154">
+        <v>4383.3</v>
+      </c>
+      <c r="BN154">
+        <v>8191.6</v>
+      </c>
+      <c r="BO154">
+        <v>10166.6</v>
+      </c>
+      <c r="BP154">
+        <v>716.6</v>
+      </c>
+      <c r="BQ154">
+        <v>162266.4</v>
+      </c>
     </row>
-    <row r="155" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A155" s="243">
         <v>2562</v>
       </c>
@@ -30518,8 +33773,29 @@
       <c r="BJ155" s="110">
         <v>18595.740000000002</v>
       </c>
+      <c r="BK155">
+        <v>100308.3</v>
+      </c>
+      <c r="BL155">
+        <v>38500</v>
+      </c>
+      <c r="BM155">
+        <v>4383.3</v>
+      </c>
+      <c r="BN155">
+        <v>8191.6</v>
+      </c>
+      <c r="BO155">
+        <v>10166.6</v>
+      </c>
+      <c r="BP155">
+        <v>716.6</v>
+      </c>
+      <c r="BQ155">
+        <v>162266.4</v>
+      </c>
     </row>
-    <row r="156" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A156" s="243">
         <v>2562</v>
       </c>
@@ -30698,8 +33974,29 @@
       <c r="BJ156" s="110">
         <v>17162.22</v>
       </c>
+      <c r="BK156">
+        <v>100308.3</v>
+      </c>
+      <c r="BL156">
+        <v>38500</v>
+      </c>
+      <c r="BM156">
+        <v>4383.3</v>
+      </c>
+      <c r="BN156">
+        <v>8191.6</v>
+      </c>
+      <c r="BO156">
+        <v>10166.6</v>
+      </c>
+      <c r="BP156">
+        <v>716.6</v>
+      </c>
+      <c r="BQ156">
+        <v>162266.4</v>
+      </c>
     </row>
-    <row r="157" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A157" s="243">
         <v>2562</v>
       </c>
@@ -30878,8 +34175,29 @@
       <c r="BJ157" s="110">
         <v>14700.88</v>
       </c>
+      <c r="BK157">
+        <v>100308.3</v>
+      </c>
+      <c r="BL157">
+        <v>38500</v>
+      </c>
+      <c r="BM157">
+        <v>4383.3</v>
+      </c>
+      <c r="BN157">
+        <v>8191.6</v>
+      </c>
+      <c r="BO157">
+        <v>10166.6</v>
+      </c>
+      <c r="BP157">
+        <v>716.6</v>
+      </c>
+      <c r="BQ157">
+        <v>162266.4</v>
+      </c>
     </row>
-    <row r="158" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A158" s="253">
         <v>2563</v>
       </c>
@@ -31058,8 +34376,29 @@
       <c r="BJ158" s="127">
         <v>13364</v>
       </c>
+      <c r="BK158">
+        <v>104183.3</v>
+      </c>
+      <c r="BL158">
+        <v>36450</v>
+      </c>
+      <c r="BM158">
+        <v>3941.6</v>
+      </c>
+      <c r="BN158">
+        <v>8308.2999999999993</v>
+      </c>
+      <c r="BO158">
+        <v>12258.3</v>
+      </c>
+      <c r="BP158">
+        <v>3958.3</v>
+      </c>
+      <c r="BQ158">
+        <v>169099.8</v>
+      </c>
     </row>
-    <row r="159" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A159" s="253">
         <v>2563</v>
       </c>
@@ -31238,8 +34577,29 @@
       <c r="BJ159" s="127">
         <v>14814.27</v>
       </c>
+      <c r="BK159">
+        <v>104183.3</v>
+      </c>
+      <c r="BL159">
+        <v>36450</v>
+      </c>
+      <c r="BM159">
+        <v>3941.6</v>
+      </c>
+      <c r="BN159">
+        <v>8308.2999999999993</v>
+      </c>
+      <c r="BO159">
+        <v>12258.3</v>
+      </c>
+      <c r="BP159">
+        <v>3958.3</v>
+      </c>
+      <c r="BQ159">
+        <v>169099.8</v>
+      </c>
     </row>
-    <row r="160" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A160" s="253">
         <v>2563</v>
       </c>
@@ -31418,8 +34778,29 @@
       <c r="BJ160" s="127">
         <v>16252.57</v>
       </c>
+      <c r="BK160">
+        <v>104183.3</v>
+      </c>
+      <c r="BL160">
+        <v>36450</v>
+      </c>
+      <c r="BM160">
+        <v>3941.6</v>
+      </c>
+      <c r="BN160">
+        <v>8308.2999999999993</v>
+      </c>
+      <c r="BO160">
+        <v>12258.3</v>
+      </c>
+      <c r="BP160">
+        <v>3958.3</v>
+      </c>
+      <c r="BQ160">
+        <v>169099.8</v>
+      </c>
     </row>
-    <row r="161" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A161" s="253">
         <v>2563</v>
       </c>
@@ -31598,8 +34979,29 @@
       <c r="BJ161" s="127">
         <v>17642.599999999999</v>
       </c>
+      <c r="BK161">
+        <v>104183.3</v>
+      </c>
+      <c r="BL161">
+        <v>36450</v>
+      </c>
+      <c r="BM161">
+        <v>3941.6</v>
+      </c>
+      <c r="BN161">
+        <v>8308.2999999999993</v>
+      </c>
+      <c r="BO161">
+        <v>12258.3</v>
+      </c>
+      <c r="BP161">
+        <v>3958.3</v>
+      </c>
+      <c r="BQ161">
+        <v>169099.8</v>
+      </c>
     </row>
-    <row r="162" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A162" s="253">
         <v>2563</v>
       </c>
@@ -31778,8 +35180,29 @@
       <c r="BJ162" s="127">
         <v>17801.13</v>
       </c>
+      <c r="BK162">
+        <v>104183.3</v>
+      </c>
+      <c r="BL162">
+        <v>36450</v>
+      </c>
+      <c r="BM162">
+        <v>3941.6</v>
+      </c>
+      <c r="BN162">
+        <v>8308.2999999999993</v>
+      </c>
+      <c r="BO162">
+        <v>12258.3</v>
+      </c>
+      <c r="BP162">
+        <v>3958.3</v>
+      </c>
+      <c r="BQ162">
+        <v>169099.8</v>
+      </c>
     </row>
-    <row r="163" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A163" s="253">
         <v>2563</v>
       </c>
@@ -31958,8 +35381,29 @@
       <c r="BJ163" s="127">
         <v>17647.41</v>
       </c>
+      <c r="BK163">
+        <v>104183.3</v>
+      </c>
+      <c r="BL163">
+        <v>36450</v>
+      </c>
+      <c r="BM163">
+        <v>3941.6</v>
+      </c>
+      <c r="BN163">
+        <v>8308.2999999999993</v>
+      </c>
+      <c r="BO163">
+        <v>12258.3</v>
+      </c>
+      <c r="BP163">
+        <v>3958.3</v>
+      </c>
+      <c r="BQ163">
+        <v>169099.8</v>
+      </c>
     </row>
-    <row r="164" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A164" s="253">
         <v>2563</v>
       </c>
@@ -32138,8 +35582,29 @@
       <c r="BJ164" s="127">
         <v>16544.27</v>
       </c>
+      <c r="BK164">
+        <v>104183.3</v>
+      </c>
+      <c r="BL164">
+        <v>36450</v>
+      </c>
+      <c r="BM164">
+        <v>3941.6</v>
+      </c>
+      <c r="BN164">
+        <v>8308.2999999999993</v>
+      </c>
+      <c r="BO164">
+        <v>12258.3</v>
+      </c>
+      <c r="BP164">
+        <v>3958.3</v>
+      </c>
+      <c r="BQ164">
+        <v>169099.8</v>
+      </c>
     </row>
-    <row r="165" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A165" s="253">
         <v>2563</v>
       </c>
@@ -32318,8 +35783,29 @@
       <c r="BJ165" s="127">
         <v>16687.810000000001</v>
       </c>
+      <c r="BK165">
+        <v>104183.3</v>
+      </c>
+      <c r="BL165">
+        <v>36450</v>
+      </c>
+      <c r="BM165">
+        <v>3941.6</v>
+      </c>
+      <c r="BN165">
+        <v>8308.2999999999993</v>
+      </c>
+      <c r="BO165">
+        <v>12258.3</v>
+      </c>
+      <c r="BP165">
+        <v>3958.3</v>
+      </c>
+      <c r="BQ165">
+        <v>169099.8</v>
+      </c>
     </row>
-    <row r="166" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A166" s="253">
         <v>2563</v>
       </c>
@@ -32498,8 +35984,29 @@
       <c r="BJ166" s="127">
         <v>17062.88</v>
       </c>
+      <c r="BK166">
+        <v>104183.3</v>
+      </c>
+      <c r="BL166">
+        <v>36450</v>
+      </c>
+      <c r="BM166">
+        <v>3941.6</v>
+      </c>
+      <c r="BN166">
+        <v>8308.2999999999993</v>
+      </c>
+      <c r="BO166">
+        <v>12258.3</v>
+      </c>
+      <c r="BP166">
+        <v>3958.3</v>
+      </c>
+      <c r="BQ166">
+        <v>169099.8</v>
+      </c>
     </row>
-    <row r="167" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A167" s="253">
         <v>2563</v>
       </c>
@@ -32678,8 +36185,29 @@
       <c r="BJ167" s="127">
         <v>17901.79</v>
       </c>
+      <c r="BK167">
+        <v>104183.3</v>
+      </c>
+      <c r="BL167">
+        <v>36450</v>
+      </c>
+      <c r="BM167">
+        <v>3941.6</v>
+      </c>
+      <c r="BN167">
+        <v>8308.2999999999993</v>
+      </c>
+      <c r="BO167">
+        <v>12258.3</v>
+      </c>
+      <c r="BP167">
+        <v>3958.3</v>
+      </c>
+      <c r="BQ167">
+        <v>169099.8</v>
+      </c>
     </row>
-    <row r="168" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A168" s="253">
         <v>2563</v>
       </c>
@@ -32858,8 +36386,29 @@
       <c r="BJ168" s="127">
         <v>16373.64</v>
       </c>
+      <c r="BK168">
+        <v>104183.3</v>
+      </c>
+      <c r="BL168">
+        <v>36450</v>
+      </c>
+      <c r="BM168">
+        <v>3941.6</v>
+      </c>
+      <c r="BN168">
+        <v>8308.2999999999993</v>
+      </c>
+      <c r="BO168">
+        <v>12258.3</v>
+      </c>
+      <c r="BP168">
+        <v>3958.3</v>
+      </c>
+      <c r="BQ168">
+        <v>169099.8</v>
+      </c>
     </row>
-    <row r="169" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A169" s="253">
         <v>2563</v>
       </c>
@@ -33038,8 +36587,29 @@
       <c r="BJ169" s="127">
         <v>14693.26</v>
       </c>
+      <c r="BK169">
+        <v>104183.3</v>
+      </c>
+      <c r="BL169">
+        <v>36450</v>
+      </c>
+      <c r="BM169">
+        <v>3941.6</v>
+      </c>
+      <c r="BN169">
+        <v>8308.2999999999993</v>
+      </c>
+      <c r="BO169">
+        <v>12258.3</v>
+      </c>
+      <c r="BP169">
+        <v>3958.3</v>
+      </c>
+      <c r="BQ169">
+        <v>169099.8</v>
+      </c>
     </row>
-    <row r="170" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A170" s="255">
         <v>2564</v>
       </c>
@@ -33218,8 +36788,29 @@
       <c r="BJ170" s="165">
         <v>13186.45</v>
       </c>
+      <c r="BK170">
+        <v>92333.3</v>
+      </c>
+      <c r="BL170">
+        <v>36816.6</v>
+      </c>
+      <c r="BM170">
+        <v>4083.3</v>
+      </c>
+      <c r="BN170">
+        <v>7691.6</v>
+      </c>
+      <c r="BO170">
+        <v>9716.6</v>
+      </c>
+      <c r="BP170">
+        <v>2658.3</v>
+      </c>
+      <c r="BQ170">
+        <v>153299.70000000001</v>
+      </c>
     </row>
-    <row r="171" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A171" s="255">
         <v>2564</v>
       </c>
@@ -33398,8 +36989,29 @@
       <c r="BJ171" s="165">
         <v>13317.76</v>
       </c>
+      <c r="BK171">
+        <v>92333.3</v>
+      </c>
+      <c r="BL171">
+        <v>36816.6</v>
+      </c>
+      <c r="BM171">
+        <v>4083.3</v>
+      </c>
+      <c r="BN171">
+        <v>7691.6</v>
+      </c>
+      <c r="BO171">
+        <v>9716.6</v>
+      </c>
+      <c r="BP171">
+        <v>2658.3</v>
+      </c>
+      <c r="BQ171">
+        <v>153299.70000000001</v>
+      </c>
     </row>
-    <row r="172" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A172" s="255">
         <v>2564</v>
       </c>
@@ -33578,8 +37190,29 @@
       <c r="BJ172" s="165">
         <v>16536.53</v>
       </c>
+      <c r="BK172">
+        <v>92333.3</v>
+      </c>
+      <c r="BL172">
+        <v>36816.6</v>
+      </c>
+      <c r="BM172">
+        <v>4083.3</v>
+      </c>
+      <c r="BN172">
+        <v>7691.6</v>
+      </c>
+      <c r="BO172">
+        <v>9716.6</v>
+      </c>
+      <c r="BP172">
+        <v>2658.3</v>
+      </c>
+      <c r="BQ172">
+        <v>153299.70000000001</v>
+      </c>
     </row>
-    <row r="173" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A173" s="255">
         <v>2564</v>
       </c>
@@ -33758,8 +37391,29 @@
       <c r="BJ173" s="165">
         <v>14891.98</v>
       </c>
+      <c r="BK173">
+        <v>92333.3</v>
+      </c>
+      <c r="BL173">
+        <v>36816.6</v>
+      </c>
+      <c r="BM173">
+        <v>4083.3</v>
+      </c>
+      <c r="BN173">
+        <v>7691.6</v>
+      </c>
+      <c r="BO173">
+        <v>9716.6</v>
+      </c>
+      <c r="BP173">
+        <v>2658.3</v>
+      </c>
+      <c r="BQ173">
+        <v>153299.70000000001</v>
+      </c>
     </row>
-    <row r="174" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A174" s="255">
         <v>2564</v>
       </c>
@@ -33938,8 +37592,29 @@
       <c r="BJ174" s="165">
         <v>14870.49</v>
       </c>
+      <c r="BK174">
+        <v>92333.3</v>
+      </c>
+      <c r="BL174">
+        <v>36816.6</v>
+      </c>
+      <c r="BM174">
+        <v>4083.3</v>
+      </c>
+      <c r="BN174">
+        <v>7691.6</v>
+      </c>
+      <c r="BO174">
+        <v>9716.6</v>
+      </c>
+      <c r="BP174">
+        <v>2658.3</v>
+      </c>
+      <c r="BQ174">
+        <v>153299.70000000001</v>
+      </c>
     </row>
-    <row r="175" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A175" s="255">
         <v>2564</v>
       </c>
@@ -34118,8 +37793,29 @@
       <c r="BJ175" s="165">
         <v>17446.96</v>
       </c>
+      <c r="BK175">
+        <v>92333.3</v>
+      </c>
+      <c r="BL175">
+        <v>36816.6</v>
+      </c>
+      <c r="BM175">
+        <v>4083.3</v>
+      </c>
+      <c r="BN175">
+        <v>7691.6</v>
+      </c>
+      <c r="BO175">
+        <v>9716.6</v>
+      </c>
+      <c r="BP175">
+        <v>2658.3</v>
+      </c>
+      <c r="BQ175">
+        <v>153299.70000000001</v>
+      </c>
     </row>
-    <row r="176" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A176" s="255">
         <v>2564</v>
       </c>
@@ -34298,8 +37994,29 @@
       <c r="BJ176" s="165">
         <v>15894.17</v>
       </c>
+      <c r="BK176">
+        <v>92333.3</v>
+      </c>
+      <c r="BL176">
+        <v>36816.6</v>
+      </c>
+      <c r="BM176">
+        <v>4083.3</v>
+      </c>
+      <c r="BN176">
+        <v>7691.6</v>
+      </c>
+      <c r="BO176">
+        <v>9716.6</v>
+      </c>
+      <c r="BP176">
+        <v>2658.3</v>
+      </c>
+      <c r="BQ176">
+        <v>153299.70000000001</v>
+      </c>
     </row>
-    <row r="177" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A177" s="255">
         <v>2564</v>
       </c>
@@ -34478,8 +38195,29 @@
       <c r="BJ177" s="165">
         <v>16024.79</v>
       </c>
+      <c r="BK177">
+        <v>92333.3</v>
+      </c>
+      <c r="BL177">
+        <v>36816.6</v>
+      </c>
+      <c r="BM177">
+        <v>4083.3</v>
+      </c>
+      <c r="BN177">
+        <v>7691.6</v>
+      </c>
+      <c r="BO177">
+        <v>9716.6</v>
+      </c>
+      <c r="BP177">
+        <v>2658.3</v>
+      </c>
+      <c r="BQ177">
+        <v>153299.70000000001</v>
+      </c>
     </row>
-    <row r="178" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A178" s="255">
         <v>2564</v>
       </c>
@@ -34658,8 +38396,29 @@
       <c r="BJ178" s="165">
         <v>17563.68</v>
       </c>
+      <c r="BK178">
+        <v>92333.3</v>
+      </c>
+      <c r="BL178">
+        <v>36816.6</v>
+      </c>
+      <c r="BM178">
+        <v>4083.3</v>
+      </c>
+      <c r="BN178">
+        <v>7691.6</v>
+      </c>
+      <c r="BO178">
+        <v>9716.6</v>
+      </c>
+      <c r="BP178">
+        <v>2658.3</v>
+      </c>
+      <c r="BQ178">
+        <v>153299.70000000001</v>
+      </c>
     </row>
-    <row r="179" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A179" s="255">
         <v>2564</v>
       </c>
@@ -34838,8 +38597,29 @@
       <c r="BJ179" s="165">
         <v>18628.79</v>
       </c>
+      <c r="BK179">
+        <v>92333.3</v>
+      </c>
+      <c r="BL179">
+        <v>36816.6</v>
+      </c>
+      <c r="BM179">
+        <v>4083.3</v>
+      </c>
+      <c r="BN179">
+        <v>7691.6</v>
+      </c>
+      <c r="BO179">
+        <v>9716.6</v>
+      </c>
+      <c r="BP179">
+        <v>2658.3</v>
+      </c>
+      <c r="BQ179">
+        <v>153299.70000000001</v>
+      </c>
     </row>
-    <row r="180" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A180" s="255">
         <v>2564</v>
       </c>
@@ -35018,8 +38798,29 @@
       <c r="BJ180" s="165">
         <v>18670.96</v>
       </c>
+      <c r="BK180">
+        <v>92333.3</v>
+      </c>
+      <c r="BL180">
+        <v>36816.6</v>
+      </c>
+      <c r="BM180">
+        <v>4083.3</v>
+      </c>
+      <c r="BN180">
+        <v>7691.6</v>
+      </c>
+      <c r="BO180">
+        <v>9716.6</v>
+      </c>
+      <c r="BP180">
+        <v>2658.3</v>
+      </c>
+      <c r="BQ180">
+        <v>153299.70000000001</v>
+      </c>
     </row>
-    <row r="181" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A181" s="255">
         <v>2564</v>
       </c>
@@ -35198,8 +38999,29 @@
       <c r="BJ181" s="165">
         <v>18186.98</v>
       </c>
+      <c r="BK181">
+        <v>92333.3</v>
+      </c>
+      <c r="BL181">
+        <v>36816.6</v>
+      </c>
+      <c r="BM181">
+        <v>4083.3</v>
+      </c>
+      <c r="BN181">
+        <v>7691.6</v>
+      </c>
+      <c r="BO181">
+        <v>9716.6</v>
+      </c>
+      <c r="BP181">
+        <v>2658.3</v>
+      </c>
+      <c r="BQ181">
+        <v>153299.70000000001</v>
+      </c>
     </row>
-    <row r="182" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A182" s="237">
         <v>2565</v>
       </c>
@@ -35378,8 +39200,29 @@
       <c r="BJ182" s="71">
         <v>15984.2</v>
       </c>
+      <c r="BK182">
+        <v>92350</v>
+      </c>
+      <c r="BL182">
+        <v>37016.6</v>
+      </c>
+      <c r="BM182">
+        <v>4283.3</v>
+      </c>
+      <c r="BN182">
+        <v>8041.6</v>
+      </c>
+      <c r="BO182">
+        <v>8650</v>
+      </c>
+      <c r="BP182">
+        <v>825</v>
+      </c>
+      <c r="BQ182">
+        <v>151166.5</v>
+      </c>
     </row>
-    <row r="183" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A183" s="237">
         <v>2565</v>
       </c>
@@ -35558,8 +39401,29 @@
       <c r="BJ183" s="71">
         <v>17619.38</v>
       </c>
+      <c r="BK183">
+        <v>92350</v>
+      </c>
+      <c r="BL183">
+        <v>37016.6</v>
+      </c>
+      <c r="BM183">
+        <v>4283.3</v>
+      </c>
+      <c r="BN183">
+        <v>8041.6</v>
+      </c>
+      <c r="BO183">
+        <v>8650</v>
+      </c>
+      <c r="BP183">
+        <v>825</v>
+      </c>
+      <c r="BQ183">
+        <v>151166.5</v>
+      </c>
     </row>
-    <row r="184" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A184" s="237">
         <v>2565</v>
       </c>
@@ -35738,8 +39602,29 @@
       <c r="BJ184" s="71">
         <v>19233.55</v>
       </c>
+      <c r="BK184">
+        <v>92350</v>
+      </c>
+      <c r="BL184">
+        <v>37016.6</v>
+      </c>
+      <c r="BM184">
+        <v>4283.3</v>
+      </c>
+      <c r="BN184">
+        <v>8041.6</v>
+      </c>
+      <c r="BO184">
+        <v>8650</v>
+      </c>
+      <c r="BP184">
+        <v>825</v>
+      </c>
+      <c r="BQ184">
+        <v>151166.5</v>
+      </c>
     </row>
-    <row r="185" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A185" s="237">
         <v>2565</v>
       </c>
@@ -35918,8 +39803,29 @@
       <c r="BJ185" s="71">
         <v>17366.38</v>
       </c>
+      <c r="BK185">
+        <v>92350</v>
+      </c>
+      <c r="BL185">
+        <v>37016.6</v>
+      </c>
+      <c r="BM185">
+        <v>4283.3</v>
+      </c>
+      <c r="BN185">
+        <v>8041.6</v>
+      </c>
+      <c r="BO185">
+        <v>8650</v>
+      </c>
+      <c r="BP185">
+        <v>825</v>
+      </c>
+      <c r="BQ185">
+        <v>151166.5</v>
+      </c>
     </row>
-    <row r="186" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A186" s="237">
         <v>2565</v>
       </c>
@@ -36098,8 +40004,29 @@
       <c r="BJ186" s="71">
         <v>18732</v>
       </c>
+      <c r="BK186">
+        <v>92350</v>
+      </c>
+      <c r="BL186">
+        <v>37016.6</v>
+      </c>
+      <c r="BM186">
+        <v>4283.3</v>
+      </c>
+      <c r="BN186">
+        <v>8041.6</v>
+      </c>
+      <c r="BO186">
+        <v>8650</v>
+      </c>
+      <c r="BP186">
+        <v>825</v>
+      </c>
+      <c r="BQ186">
+        <v>151166.5</v>
+      </c>
     </row>
-    <row r="187" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A187" s="237">
         <v>2565</v>
       </c>
@@ -36278,8 +40205,29 @@
       <c r="BJ187" s="71">
         <v>19982.939999999999</v>
       </c>
+      <c r="BK187">
+        <v>92350</v>
+      </c>
+      <c r="BL187">
+        <v>37016.6</v>
+      </c>
+      <c r="BM187">
+        <v>4283.3</v>
+      </c>
+      <c r="BN187">
+        <v>8041.6</v>
+      </c>
+      <c r="BO187">
+        <v>8650</v>
+      </c>
+      <c r="BP187">
+        <v>825</v>
+      </c>
+      <c r="BQ187">
+        <v>151166.5</v>
+      </c>
     </row>
-    <row r="188" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A188" s="237">
         <v>2565</v>
       </c>
@@ -36458,8 +40406,29 @@
       <c r="BJ188" s="71">
         <v>19448.78</v>
       </c>
+      <c r="BK188">
+        <v>92350</v>
+      </c>
+      <c r="BL188">
+        <v>37016.6</v>
+      </c>
+      <c r="BM188">
+        <v>4283.3</v>
+      </c>
+      <c r="BN188">
+        <v>8041.6</v>
+      </c>
+      <c r="BO188">
+        <v>8650</v>
+      </c>
+      <c r="BP188">
+        <v>825</v>
+      </c>
+      <c r="BQ188">
+        <v>151166.5</v>
+      </c>
     </row>
-    <row r="189" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A189" s="237">
         <v>2565</v>
       </c>
@@ -36638,8 +40607,29 @@
       <c r="BJ189" s="71">
         <v>20503.32</v>
       </c>
+      <c r="BK189">
+        <v>92350</v>
+      </c>
+      <c r="BL189">
+        <v>37016.6</v>
+      </c>
+      <c r="BM189">
+        <v>4283.3</v>
+      </c>
+      <c r="BN189">
+        <v>8041.6</v>
+      </c>
+      <c r="BO189">
+        <v>8650</v>
+      </c>
+      <c r="BP189">
+        <v>825</v>
+      </c>
+      <c r="BQ189">
+        <v>151166.5</v>
+      </c>
     </row>
-    <row r="190" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A190" s="237">
         <v>2565</v>
       </c>
@@ -36818,8 +40808,29 @@
       <c r="BJ190" s="71">
         <v>21304.65</v>
       </c>
+      <c r="BK190">
+        <v>92350</v>
+      </c>
+      <c r="BL190">
+        <v>37016.6</v>
+      </c>
+      <c r="BM190">
+        <v>4283.3</v>
+      </c>
+      <c r="BN190">
+        <v>8041.6</v>
+      </c>
+      <c r="BO190">
+        <v>8650</v>
+      </c>
+      <c r="BP190">
+        <v>825</v>
+      </c>
+      <c r="BQ190">
+        <v>151166.5</v>
+      </c>
     </row>
-    <row r="191" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A191" s="237">
         <v>2565</v>
       </c>
@@ -36998,8 +41009,29 @@
       <c r="BJ191" s="71">
         <v>19590.810000000001</v>
       </c>
+      <c r="BK191">
+        <v>92350</v>
+      </c>
+      <c r="BL191">
+        <v>37016.6</v>
+      </c>
+      <c r="BM191">
+        <v>4283.3</v>
+      </c>
+      <c r="BN191">
+        <v>8041.6</v>
+      </c>
+      <c r="BO191">
+        <v>8650</v>
+      </c>
+      <c r="BP191">
+        <v>825</v>
+      </c>
+      <c r="BQ191">
+        <v>151166.5</v>
+      </c>
     </row>
-    <row r="192" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A192" s="237">
         <v>2565</v>
       </c>
@@ -37178,8 +41210,29 @@
       <c r="BJ192" s="71">
         <v>20400.349999999999</v>
       </c>
+      <c r="BK192">
+        <v>92350</v>
+      </c>
+      <c r="BL192">
+        <v>37016.6</v>
+      </c>
+      <c r="BM192">
+        <v>4283.3</v>
+      </c>
+      <c r="BN192">
+        <v>8041.6</v>
+      </c>
+      <c r="BO192">
+        <v>8650</v>
+      </c>
+      <c r="BP192">
+        <v>825</v>
+      </c>
+      <c r="BQ192">
+        <v>151166.5</v>
+      </c>
     </row>
-    <row r="193" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A193" s="237">
         <v>2565</v>
       </c>
@@ -37358,8 +41411,29 @@
       <c r="BJ193" s="71">
         <v>18917.96</v>
       </c>
+      <c r="BK193">
+        <v>92350</v>
+      </c>
+      <c r="BL193">
+        <v>37016.6</v>
+      </c>
+      <c r="BM193">
+        <v>4283.3</v>
+      </c>
+      <c r="BN193">
+        <v>8041.6</v>
+      </c>
+      <c r="BO193">
+        <v>8650</v>
+      </c>
+      <c r="BP193">
+        <v>825</v>
+      </c>
+      <c r="BQ193">
+        <v>151166.5</v>
+      </c>
     </row>
-    <row r="194" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A194" s="256">
         <v>2566</v>
       </c>
@@ -37543,7 +41617,7 @@
         <v>14231.17</v>
       </c>
     </row>
-    <row r="195" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A195" s="256">
         <v>2566</v>
       </c>
@@ -37727,7 +41801,7 @@
         <v>15790.87</v>
       </c>
     </row>
-    <row r="196" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A196" s="256">
         <v>2566</v>
       </c>
@@ -37911,7 +41985,7 @@
         <v>18347.82</v>
       </c>
     </row>
-    <row r="197" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A197" s="256">
         <v>2566</v>
       </c>
@@ -38095,7 +42169,7 @@
         <v>15005.84</v>
       </c>
     </row>
-    <row r="198" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A198" s="256">
         <v>2566</v>
       </c>
@@ -38279,7 +42353,7 @@
         <v>18600.18</v>
       </c>
     </row>
-    <row r="199" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A199" s="256">
         <v>2566</v>
       </c>
@@ -38463,7 +42537,7 @@
         <v>17836.32</v>
       </c>
     </row>
-    <row r="200" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A200" s="256">
         <v>2566</v>
       </c>
@@ -38647,7 +42721,7 @@
         <v>17644.12</v>
       </c>
     </row>
-    <row r="201" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A201" s="256">
         <v>2566</v>
       </c>
@@ -38831,7 +42905,7 @@
         <v>17943.28</v>
       </c>
     </row>
-    <row r="202" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A202" s="256">
         <v>2566</v>
       </c>
@@ -39015,7 +43089,7 @@
         <v>18910.919999999998</v>
       </c>
     </row>
-    <row r="203" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A203" s="256">
         <v>2566</v>
       </c>
@@ -39199,7 +43273,7 @@
         <v>19164.41</v>
       </c>
     </row>
-    <row r="204" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A204" s="256">
         <v>2566</v>
       </c>
@@ -39383,7 +43457,7 @@
         <v>20329.53</v>
       </c>
     </row>
-    <row r="205" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A205" s="256">
         <v>2566</v>
       </c>
@@ -39567,7 +43641,7 @@
         <v>17481.09</v>
       </c>
     </row>
-    <row r="206" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A206" s="243">
         <v>2567</v>
       </c>
@@ -39747,7 +43821,7 @@
         <v>17136.61</v>
       </c>
     </row>
-    <row r="207" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A207" s="243">
         <v>2567</v>
       </c>
@@ -39927,7 +44001,7 @@
         <v>19243.61</v>
       </c>
     </row>
-    <row r="208" spans="1:62" ht="21" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:69" ht="21" x14ac:dyDescent="0.3">
       <c r="A208" s="243">
         <v>2567</v>
       </c>
